--- a/reports/Master_Retention_Summary.xlsx
+++ b/reports/Master_Retention_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3004,6 +3004,1062 @@
         <v>98.31746131483692</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>54</v>
+      </c>
+      <c r="B108" t="n">
+        <v>1.081899814711346</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1.081899814711346</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>98.35452861012236</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>55</v>
+      </c>
+      <c r="B109" t="n">
+        <v>2.197097286667498</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1.115197471956152</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>101.3815883596502</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>56</v>
+      </c>
+      <c r="B110" t="n">
+        <v>3.311716486578501</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1.114619199911003</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>101.3290181737275</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>57</v>
+      </c>
+      <c r="B111" t="n">
+        <v>4.427603441525903</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1.115886954947402</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>101.444268631582</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>58</v>
+      </c>
+      <c r="B112" t="n">
+        <v>5.540984094839137</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1.113380653313234</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>101.2164230284758</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>59</v>
+      </c>
+      <c r="B113" t="n">
+        <v>6.532350218635037</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.9913661237958999</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>90.12419307235453</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>60</v>
+      </c>
+      <c r="B114" t="n">
+        <v>7.638404628890744</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1.106054410255707</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>100.550400932337</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>61</v>
+      </c>
+      <c r="B115" t="n">
+        <v>8.741539806756558</v>
+      </c>
+      <c r="C115" t="n">
+        <v>1.103135177865814</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>100.2850161696194</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>62</v>
+      </c>
+      <c r="B116" t="n">
+        <v>9.841185502031855</v>
+      </c>
+      <c r="C116" t="n">
+        <v>1.099645695275298</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>99.9677904795725</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>63</v>
+      </c>
+      <c r="B117" t="n">
+        <v>10.93642854049193</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.095243038460071</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>99.56754895091551</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>64</v>
+      </c>
+      <c r="B118" t="n">
+        <v>12.03253652656832</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.09610798607639</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>99.64618055239912</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>65</v>
+      </c>
+      <c r="B119" t="n">
+        <v>13.12588819125543</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1.093351664687116</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>99.39560588064693</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>66</v>
+      </c>
+      <c r="B120" t="n">
+        <v>14.21452451527082</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.08863632401539</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>98.96693854685361</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>67</v>
+      </c>
+      <c r="B121" t="n">
+        <v>15.30180766500564</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1.087283149734816</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>98.84392270316508</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>68</v>
+      </c>
+      <c r="B122" t="n">
+        <v>16.38749283081446</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.085685165808824</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>98.69865143716584</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>69</v>
+      </c>
+      <c r="B123" t="n">
+        <v>17.47161112865763</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.084118297843169</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>98.55620889483353</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>70</v>
+      </c>
+      <c r="B124" t="n">
+        <v>18.55366510164228</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.082053972984646</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>98.36854299860417</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>71</v>
+      </c>
+      <c r="B125" t="n">
+        <v>19.63655386866763</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.082888767025352</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>98.44443336594109</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>72</v>
+      </c>
+      <c r="B126" t="n">
+        <v>20.71812767692838</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.081573808260753</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>98.32489166006846</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>73</v>
+      </c>
+      <c r="B127" t="n">
+        <v>21.79609390895809</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1.077966232029709</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>97.99693018451902</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>74</v>
+      </c>
+      <c r="B128" t="n">
+        <v>22.87346368866534</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1.077369779707251</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>97.9427072461137</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>75</v>
+      </c>
+      <c r="B129" t="n">
+        <v>23.95007205567908</v>
+      </c>
+      <c r="C129" t="n">
+        <v>1.076608367013733</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>97.87348791033939</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>76</v>
+      </c>
+      <c r="B130" t="n">
+        <v>25.02522698626506</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1.075154930585985</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>97.74135732599861</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>77</v>
+      </c>
+      <c r="B131" t="n">
+        <v>26.10007439596228</v>
+      </c>
+      <c r="C131" t="n">
+        <v>1.07484740969722</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>97.71340088156548</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>78</v>
+      </c>
+      <c r="B132" t="n">
+        <v>27.17632729862558</v>
+      </c>
+      <c r="C132" t="n">
+        <v>1.076252902663295</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>97.84117296939048</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>79</v>
+      </c>
+      <c r="B133" t="n">
+        <v>28.25176394808324</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1.075436649457661</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>97.76696813251461</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>80</v>
+      </c>
+      <c r="B134" t="n">
+        <v>29.32644450177206</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.074680553688822</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>97.69823215352925</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>81</v>
+      </c>
+      <c r="B135" t="n">
+        <v>30.40055977344338</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1.074115271671321</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>97.64684287921098</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>82</v>
+      </c>
+      <c r="B136" t="n">
+        <v>31.35564237082223</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.9550825973788513</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>86.82569067080466</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>83</v>
+      </c>
+      <c r="B137" t="n">
+        <v>32.31278397513493</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.9571416043126959</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>87.01287311933599</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>84</v>
+      </c>
+      <c r="B138" t="n">
+        <v>33.3882989452408</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1.075514970105871</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>97.77408819144283</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>85</v>
+      </c>
+      <c r="B139" t="n">
+        <v>34.46035574771486</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1.072056802474066</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>97.45970931582416</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>86</v>
+      </c>
+      <c r="B140" t="n">
+        <v>35.53164235297993</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1.071286605265065</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>97.38969138773321</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>87</v>
+      </c>
+      <c r="B141" t="n">
+        <v>36.60218658027386</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1.070544227293929</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>97.3222024812663</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>88</v>
+      </c>
+      <c r="B142" t="n">
+        <v>37.55217690476263</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.9499903244887662</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>86.362756771706</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>89</v>
+      </c>
+      <c r="B143" t="n">
+        <v>38.62419898943297</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.072022084670344</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>97.45655315184946</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>90</v>
+      </c>
+      <c r="B144" t="n">
+        <v>39.69325441973722</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1.069055430304246</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>97.186857300386</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>91</v>
+      </c>
+      <c r="B145" t="n">
+        <v>40.76224224931294</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1.068987829575725</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>97.18071177961139</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>92</v>
+      </c>
+      <c r="B146" t="n">
+        <v>41.83011469306678</v>
+      </c>
+      <c r="C146" t="n">
+        <v>1.067872443753842</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>97.07931306853109</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>93</v>
+      </c>
+      <c r="B147" t="n">
+        <v>42.89740927512767</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1.067294582060889</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>97.02678018735352</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>94</v>
+      </c>
+      <c r="B148" t="n">
+        <v>43.96223453172722</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1.064825256599548</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>96.80229605450434</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>95</v>
+      </c>
+      <c r="B149" t="n">
+        <v>45.02199540476474</v>
+      </c>
+      <c r="C149" t="n">
+        <v>1.059760873037519</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>96.34189754886532</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>96</v>
+      </c>
+      <c r="B150" t="n">
+        <v>46.08053865316903</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1.058543248404291</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>96.2312044003901</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>97</v>
+      </c>
+      <c r="B151" t="n">
+        <v>47.13797982069934</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1.057441167530314</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>96.13101523002852</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/Master_Retention_Summary.xlsx
+++ b/reports/Master_Retention_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4060,6 +4060,1350 @@
         <v>96.13101523002852</v>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>1</v>
+      </c>
+      <c r="B152" t="n">
+        <v>1.153332504667897</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1.153332504667897</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>104.8484095152634</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>2</v>
+      </c>
+      <c r="B153" t="n">
+        <v>1.134444845802931</v>
+      </c>
+      <c r="C153" t="n">
+        <v>1.134444845802931</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>103.1313496184483</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>3</v>
+      </c>
+      <c r="B154" t="n">
+        <v>1.133098066392579</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1.133098066392579</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>103.0089151265981</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>1</v>
+      </c>
+      <c r="B155" t="n">
+        <v>1.16241194625815</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1.16241194625815</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>105.6738132961954</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>2</v>
+      </c>
+      <c r="B156" t="n">
+        <v>1.140773820517232</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1.140773820517232</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>103.706710956112</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>3</v>
+      </c>
+      <c r="B157" t="n">
+        <v>1.139105930615482</v>
+      </c>
+      <c r="C157" t="n">
+        <v>1.139105930615482</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>103.5550846014075</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>4</v>
+      </c>
+      <c r="B158" t="n">
+        <v>1.138543595376723</v>
+      </c>
+      <c r="C158" t="n">
+        <v>1.138543595376723</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>103.5039632160657</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>5</v>
+      </c>
+      <c r="B159" t="n">
+        <v>2.276498796615165</v>
+      </c>
+      <c r="C159" t="n">
+        <v>1.137955201238442</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>103.4504728398584</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>6</v>
+      </c>
+      <c r="B160" t="n">
+        <v>3.413179106350995</v>
+      </c>
+      <c r="C160" t="n">
+        <v>1.13668030973583</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>103.3345736123482</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>7</v>
+      </c>
+      <c r="B161" t="n">
+        <v>4.547398499644769</v>
+      </c>
+      <c r="C161" t="n">
+        <v>1.134219393293774</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>103.1108539357977</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>8</v>
+      </c>
+      <c r="B162" t="n">
+        <v>5.671115152841734</v>
+      </c>
+      <c r="C162" t="n">
+        <v>1.123716653196965</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>102.1560593815423</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>9</v>
+      </c>
+      <c r="B163" t="n">
+        <v>6.785802736033912</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1.114687583192178</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>101.3352348356525</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>10</v>
+      </c>
+      <c r="B164" t="n">
+        <v>7.896140661276919</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1.110337925243007</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>100.9398113857279</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>11</v>
+      </c>
+      <c r="B165" t="n">
+        <v>9.003128063043921</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1.106987401767001</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>100.6352183424546</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>12</v>
+      </c>
+      <c r="B166" t="n">
+        <v>10.10719936217718</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1.104071299133263</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>100.3701181030239</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>13</v>
+      </c>
+      <c r="B167" t="n">
+        <v>11.21830930616636</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1.111109943989181</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>101.0099949081074</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>14</v>
+      </c>
+      <c r="B168" t="n">
+        <v>12.33129184444021</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1.112982538273844</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>101.1802307521676</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>15</v>
+      </c>
+      <c r="B169" t="n">
+        <v>13.44429821496854</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1.113006370528336</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>101.1823973207578</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>16</v>
+      </c>
+      <c r="B170" t="n">
+        <v>14.55696321107396</v>
+      </c>
+      <c r="C170" t="n">
+        <v>1.112664996105419</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>101.1513632823108</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>17</v>
+      </c>
+      <c r="B171" t="n">
+        <v>15.66905977805289</v>
+      </c>
+      <c r="C171" t="n">
+        <v>1.112096566978929</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>101.0996879071753</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>18</v>
+      </c>
+      <c r="B172" t="n">
+        <v>16.78078183103145</v>
+      </c>
+      <c r="C172" t="n">
+        <v>1.111722052978559</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>101.065641179869</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>19</v>
+      </c>
+      <c r="B173" t="n">
+        <v>17.8917186480297</v>
+      </c>
+      <c r="C173" t="n">
+        <v>1.110936816998251</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>100.9942560907501</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>20</v>
+      </c>
+      <c r="B174" t="n">
+        <v>19.00215402491973</v>
+      </c>
+      <c r="C174" t="n">
+        <v>1.110435376890031</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>100.9486706263665</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>21</v>
+      </c>
+      <c r="B175" t="n">
+        <v>20.11174053883676</v>
+      </c>
+      <c r="C175" t="n">
+        <v>1.10958651391703</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>100.8715012651845</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>22</v>
+      </c>
+      <c r="B176" t="n">
+        <v>21.22055567953404</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1.108815140697281</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>100.8013764270256</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>23</v>
+      </c>
+      <c r="B177" t="n">
+        <v>22.32876013317005</v>
+      </c>
+      <c r="C177" t="n">
+        <v>1.108204453636006</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>100.7458594214551</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>24</v>
+      </c>
+      <c r="B178" t="n">
+        <v>23.43637941065311</v>
+      </c>
+      <c r="C178" t="n">
+        <v>1.10761927748306</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>100.6926615893691</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>25</v>
+      </c>
+      <c r="B179" t="n">
+        <v>24.54330866647413</v>
+      </c>
+      <c r="C179" t="n">
+        <v>1.106929255821022</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>100.6299323473656</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>26</v>
+      </c>
+      <c r="B180" t="n">
+        <v>25.64969708119986</v>
+      </c>
+      <c r="C180" t="n">
+        <v>1.106388414725725</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>100.5807649750659</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>27</v>
+      </c>
+      <c r="B181" t="n">
+        <v>26.75530855498607</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1.105611473786208</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>100.5101339805644</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>28</v>
+      </c>
+      <c r="B182" t="n">
+        <v>27.8584226802503</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1.103114125264234</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>100.2831022967486</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>29</v>
+      </c>
+      <c r="B183" t="n">
+        <v>28.94836323080262</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1.089940550552317</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>99.08550459566517</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>30</v>
+      </c>
+      <c r="B184" t="n">
+        <v>30.03335032605572</v>
+      </c>
+      <c r="C184" t="n">
+        <v>1.084987095253105</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>98.63519047755499</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>31</v>
+      </c>
+      <c r="B185" t="n">
+        <v>31.11533872147519</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1.081988395419472</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>98.3625814017702</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>32</v>
+      </c>
+      <c r="B186" t="n">
+        <v>32.19464481784028</v>
+      </c>
+      <c r="C186" t="n">
+        <v>1.079306096365091</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>98.11873603319007</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>33</v>
+      </c>
+      <c r="B187" t="n">
+        <v>33.27351385051168</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1.078869032671392</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>98.07900297012652</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>34</v>
+      </c>
+      <c r="B188" t="n">
+        <v>34.36338568439516</v>
+      </c>
+      <c r="C188" t="n">
+        <v>1.089871833883485</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>99.07925762577139</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>35</v>
+      </c>
+      <c r="B189" t="n">
+        <v>35.45332968915602</v>
+      </c>
+      <c r="C189" t="n">
+        <v>1.089944004760859</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>99.08581861462356</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>36</v>
+      </c>
+      <c r="B190" t="n">
+        <v>36.53058146010321</v>
+      </c>
+      <c r="C190" t="n">
+        <v>1.077251770947186</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>97.93197917701687</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>37</v>
+      </c>
+      <c r="B191" t="n">
+        <v>37.60209236610033</v>
+      </c>
+      <c r="C191" t="n">
+        <v>1.071510905997123</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>97.41008236337477</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>38</v>
+      </c>
+      <c r="B192" t="n">
+        <v>38.67384202696605</v>
+      </c>
+      <c r="C192" t="n">
+        <v>1.07174966086572</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>97.43178735142908</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>39</v>
+      </c>
+      <c r="B193" t="n">
+        <v>39.74377372914694</v>
+      </c>
+      <c r="C193" t="n">
+        <v>1.069931702180888</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>97.26651838008073</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>40</v>
+      </c>
+      <c r="B194" t="n">
+        <v>40.81482844298118</v>
+      </c>
+      <c r="C194" t="n">
+        <v>1.071054713834243</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>97.36861034856757</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>41</v>
+      </c>
+      <c r="B195" t="n">
+        <v>41.89605911253297</v>
+      </c>
+      <c r="C195" t="n">
+        <v>1.081230669551793</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>98.2936972319812</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>42</v>
+      </c>
+      <c r="B196" t="n">
+        <v>42.97723465631597</v>
+      </c>
+      <c r="C196" t="n">
+        <v>1.081175543782997</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>98.2886857984543</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>43</v>
+      </c>
+      <c r="B197" t="n">
+        <v>44.04587416026572</v>
+      </c>
+      <c r="C197" t="n">
+        <v>1.068639503949747</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>97.14904581361336</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>44</v>
+      </c>
+      <c r="B198" t="n">
+        <v>45.11145101693138</v>
+      </c>
+      <c r="C198" t="n">
+        <v>1.065576856665658</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>96.8706233332416</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>45</v>
+      </c>
+      <c r="B199" t="n">
+        <v>46.17707228063038</v>
+      </c>
+      <c r="C199" t="n">
+        <v>1.065621263699001</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>96.87466033627277</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>46</v>
+      </c>
+      <c r="B200" t="n">
+        <v>47.24233115472096</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1.065258874090581</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>96.84171582641648</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>47</v>
+      </c>
+      <c r="B201" t="n">
+        <v>48.30578414269559</v>
+      </c>
+      <c r="C201" t="n">
+        <v>1.063452987974628</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>96.67754436132982</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>48</v>
+      </c>
+      <c r="B202" t="n">
+        <v>49.37966443932519</v>
+      </c>
+      <c r="C202" t="n">
+        <v>1.073880296629603</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>97.62548151178213</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>49</v>
+      </c>
+      <c r="B203" t="n">
+        <v>50.45417232904504</v>
+      </c>
+      <c r="C203" t="n">
+        <v>1.074507889719854</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>97.68253542907762</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>50</v>
+      </c>
+      <c r="B204" t="n">
+        <v>51.51861887799857</v>
+      </c>
+      <c r="C204" t="n">
+        <v>1.064446548953526</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>96.76786808668422</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>51</v>
+      </c>
+      <c r="B205" t="n">
+        <v>52.57995435510261</v>
+      </c>
+      <c r="C205" t="n">
+        <v>1.061335477104045</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>96.48504337309498</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>52</v>
+      </c>
+      <c r="B206" t="n">
+        <v>53.6398951031152</v>
+      </c>
+      <c r="C206" t="n">
+        <v>1.059940748012586</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>96.35824981932602</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>53</v>
+      </c>
+      <c r="B207" t="n">
+        <v>54.69869301159702</v>
+      </c>
+      <c r="C207" t="n">
+        <v>1.058797908481822</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>96.25435531652923</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/Master_Retention_Summary.xlsx
+++ b/reports/Master_Retention_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F207"/>
+  <dimension ref="A1:F163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3006,17 +3006,17 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="B108" t="n">
-        <v>1.081899814711346</v>
+        <v>1.153332504667897</v>
       </c>
       <c r="C108" t="n">
-        <v>1.081899814711346</v>
+        <v>1.153332504667897</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_37</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3025,22 +3025,22 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>98.35452861012236</v>
+        <v>104.8484095152634</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="B109" t="n">
-        <v>2.197097286667498</v>
+        <v>1.134444845802931</v>
       </c>
       <c r="C109" t="n">
-        <v>1.115197471956152</v>
+        <v>1.134444845802931</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_37</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3049,22 +3049,22 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>101.3815883596502</v>
+        <v>103.1313496184483</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="B110" t="n">
-        <v>3.311716486578501</v>
+        <v>1.133098066392579</v>
       </c>
       <c r="C110" t="n">
-        <v>1.114619199911003</v>
+        <v>1.133098066392579</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_37</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3073,22 +3073,22 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>101.3290181737275</v>
+        <v>103.0089151265981</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="B111" t="n">
-        <v>4.427603441525903</v>
+        <v>1.16241194625815</v>
       </c>
       <c r="C111" t="n">
-        <v>1.115886954947402</v>
+        <v>1.16241194625815</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3097,22 +3097,22 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>101.444268631582</v>
+        <v>105.6738132961954</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="B112" t="n">
-        <v>5.540984094839137</v>
+        <v>1.140773820517232</v>
       </c>
       <c r="C112" t="n">
-        <v>1.113380653313234</v>
+        <v>1.140773820517232</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -3121,22 +3121,22 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>101.2164230284758</v>
+        <v>103.706710956112</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="B113" t="n">
-        <v>6.532350218635037</v>
+        <v>1.139105930615482</v>
       </c>
       <c r="C113" t="n">
-        <v>0.9913661237958999</v>
+        <v>1.139105930615482</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3145,22 +3145,22 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>90.12419307235453</v>
+        <v>103.5550846014075</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="B114" t="n">
-        <v>7.638404628890744</v>
+        <v>1.138543595376723</v>
       </c>
       <c r="C114" t="n">
-        <v>1.106054410255707</v>
+        <v>1.138543595376723</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -3169,22 +3169,22 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>100.550400932337</v>
+        <v>103.5039632160657</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="B115" t="n">
-        <v>8.741539806756558</v>
+        <v>2.276498796615165</v>
       </c>
       <c r="C115" t="n">
-        <v>1.103135177865814</v>
+        <v>1.137955201238442</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3193,22 +3193,22 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>100.2850161696194</v>
+        <v>103.4504728398584</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="B116" t="n">
-        <v>9.841185502031855</v>
+        <v>3.413179106350995</v>
       </c>
       <c r="C116" t="n">
-        <v>1.099645695275298</v>
+        <v>1.13668030973583</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -3217,22 +3217,22 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>99.9677904795725</v>
+        <v>103.3345736123482</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="B117" t="n">
-        <v>10.93642854049193</v>
+        <v>4.547398499644769</v>
       </c>
       <c r="C117" t="n">
-        <v>1.095243038460071</v>
+        <v>1.134219393293774</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -3241,22 +3241,22 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>99.56754895091551</v>
+        <v>103.1108539357977</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="B118" t="n">
-        <v>12.03253652656832</v>
+        <v>5.671115152841734</v>
       </c>
       <c r="C118" t="n">
-        <v>1.09610798607639</v>
+        <v>1.123716653196965</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -3265,22 +3265,22 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>99.64618055239912</v>
+        <v>102.1560593815423</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="B119" t="n">
-        <v>13.12588819125543</v>
+        <v>6.785802736033912</v>
       </c>
       <c r="C119" t="n">
-        <v>1.093351664687116</v>
+        <v>1.114687583192178</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -3289,22 +3289,22 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>99.39560588064693</v>
+        <v>101.3352348356525</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="B120" t="n">
-        <v>14.21452451527082</v>
+        <v>7.896140661276919</v>
       </c>
       <c r="C120" t="n">
-        <v>1.08863632401539</v>
+        <v>1.110337925243007</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -3313,22 +3313,22 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>98.96693854685361</v>
+        <v>100.9398113857279</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="B121" t="n">
-        <v>15.30180766500564</v>
+        <v>9.003128063043921</v>
       </c>
       <c r="C121" t="n">
-        <v>1.087283149734816</v>
+        <v>1.106987401767001</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -3337,22 +3337,22 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>98.84392270316508</v>
+        <v>100.6352183424546</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="B122" t="n">
-        <v>16.38749283081446</v>
+        <v>10.10719936217718</v>
       </c>
       <c r="C122" t="n">
-        <v>1.085685165808824</v>
+        <v>1.104071299133263</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -3361,22 +3361,22 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>98.69865143716584</v>
+        <v>100.3701181030239</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="B123" t="n">
-        <v>17.47161112865763</v>
+        <v>11.21830930616636</v>
       </c>
       <c r="C123" t="n">
-        <v>1.084118297843169</v>
+        <v>1.111109943989181</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -3385,22 +3385,22 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>98.55620889483353</v>
+        <v>101.0099949081074</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="B124" t="n">
-        <v>18.55366510164228</v>
+        <v>12.33129184444021</v>
       </c>
       <c r="C124" t="n">
-        <v>1.082053972984646</v>
+        <v>1.112982538273844</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3409,22 +3409,22 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>98.36854299860417</v>
+        <v>101.1802307521676</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="B125" t="n">
-        <v>19.63655386866763</v>
+        <v>13.44429821496854</v>
       </c>
       <c r="C125" t="n">
-        <v>1.082888767025352</v>
+        <v>1.113006370528336</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -3433,22 +3433,22 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>98.44443336594109</v>
+        <v>101.1823973207578</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="B126" t="n">
-        <v>20.71812767692838</v>
+        <v>14.55696321107396</v>
       </c>
       <c r="C126" t="n">
-        <v>1.081573808260753</v>
+        <v>1.112664996105419</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -3457,22 +3457,22 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>98.32489166006846</v>
+        <v>101.1513632823108</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="B127" t="n">
-        <v>21.79609390895809</v>
+        <v>15.66905977805289</v>
       </c>
       <c r="C127" t="n">
-        <v>1.077966232029709</v>
+        <v>1.112096566978929</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -3481,22 +3481,22 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>97.99693018451902</v>
+        <v>101.0996879071753</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="B128" t="n">
-        <v>22.87346368866534</v>
+        <v>16.78078183103145</v>
       </c>
       <c r="C128" t="n">
-        <v>1.077369779707251</v>
+        <v>1.111722052978559</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -3505,22 +3505,22 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>97.9427072461137</v>
+        <v>101.065641179869</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="B129" t="n">
-        <v>23.95007205567908</v>
+        <v>17.8917186480297</v>
       </c>
       <c r="C129" t="n">
-        <v>1.076608367013733</v>
+        <v>1.110936816998251</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -3529,22 +3529,22 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>97.87348791033939</v>
+        <v>100.9942560907501</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="B130" t="n">
-        <v>25.02522698626506</v>
+        <v>19.00215402491973</v>
       </c>
       <c r="C130" t="n">
-        <v>1.075154930585985</v>
+        <v>1.110435376890031</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -3553,22 +3553,22 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>97.74135732599861</v>
+        <v>100.9486706263665</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="B131" t="n">
-        <v>26.10007439596228</v>
+        <v>20.11174053883676</v>
       </c>
       <c r="C131" t="n">
-        <v>1.07484740969722</v>
+        <v>1.10958651391703</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -3577,22 +3577,22 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>97.71340088156548</v>
+        <v>100.8715012651845</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="B132" t="n">
-        <v>27.17632729862558</v>
+        <v>21.22055567953404</v>
       </c>
       <c r="C132" t="n">
-        <v>1.076252902663295</v>
+        <v>1.108815140697281</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -3601,22 +3601,22 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>97.84117296939048</v>
+        <v>100.8013764270256</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="B133" t="n">
-        <v>28.25176394808324</v>
+        <v>22.32876013317005</v>
       </c>
       <c r="C133" t="n">
-        <v>1.075436649457661</v>
+        <v>1.108204453636006</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -3625,22 +3625,22 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>97.76696813251461</v>
+        <v>100.7458594214551</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="B134" t="n">
-        <v>29.32644450177206</v>
+        <v>23.43637941065311</v>
       </c>
       <c r="C134" t="n">
-        <v>1.074680553688822</v>
+        <v>1.10761927748306</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -3649,22 +3649,22 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>97.69823215352925</v>
+        <v>100.6926615893691</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="B135" t="n">
-        <v>30.40055977344338</v>
+        <v>24.54330866647413</v>
       </c>
       <c r="C135" t="n">
-        <v>1.074115271671321</v>
+        <v>1.106929255821022</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -3673,22 +3673,22 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>97.64684287921098</v>
+        <v>100.6299323473656</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="B136" t="n">
-        <v>31.35564237082223</v>
+        <v>25.64969708119986</v>
       </c>
       <c r="C136" t="n">
-        <v>0.9550825973788513</v>
+        <v>1.106388414725725</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -3697,22 +3697,22 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>86.82569067080466</v>
+        <v>100.5807649750659</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="B137" t="n">
-        <v>32.31278397513493</v>
+        <v>26.75530855498607</v>
       </c>
       <c r="C137" t="n">
-        <v>0.9571416043126959</v>
+        <v>1.105611473786208</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -3721,22 +3721,22 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>87.01287311933599</v>
+        <v>100.5101339805644</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="B138" t="n">
-        <v>33.3882989452408</v>
+        <v>27.8584226802503</v>
       </c>
       <c r="C138" t="n">
-        <v>1.075514970105871</v>
+        <v>1.103114125264234</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -3745,22 +3745,22 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>97.77408819144283</v>
+        <v>100.2831022967486</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="B139" t="n">
-        <v>34.46035574771486</v>
+        <v>28.94836323080262</v>
       </c>
       <c r="C139" t="n">
-        <v>1.072056802474066</v>
+        <v>1.089940550552317</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -3769,22 +3769,22 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>97.45970931582416</v>
+        <v>99.08550459566517</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="B140" t="n">
-        <v>35.53164235297993</v>
+        <v>30.03335032605572</v>
       </c>
       <c r="C140" t="n">
-        <v>1.071286605265065</v>
+        <v>1.084987095253105</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -3793,22 +3793,22 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>97.38969138773321</v>
+        <v>98.63519047755499</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="B141" t="n">
-        <v>36.60218658027386</v>
+        <v>31.11533872147519</v>
       </c>
       <c r="C141" t="n">
-        <v>1.070544227293929</v>
+        <v>1.081988395419472</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -3817,22 +3817,22 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>97.3222024812663</v>
+        <v>98.3625814017702</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="B142" t="n">
-        <v>37.55217690476263</v>
+        <v>32.19464481784028</v>
       </c>
       <c r="C142" t="n">
-        <v>0.9499903244887662</v>
+        <v>1.079306096365091</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -3841,22 +3841,22 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>86.362756771706</v>
+        <v>98.11873603319007</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="B143" t="n">
-        <v>38.62419898943297</v>
+        <v>33.27351385051168</v>
       </c>
       <c r="C143" t="n">
-        <v>1.072022084670344</v>
+        <v>1.078869032671392</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -3865,22 +3865,22 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>97.45655315184946</v>
+        <v>98.07900297012652</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="B144" t="n">
-        <v>39.69325441973722</v>
+        <v>34.36338568439516</v>
       </c>
       <c r="C144" t="n">
-        <v>1.069055430304246</v>
+        <v>1.089871833883485</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -3889,22 +3889,22 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>97.186857300386</v>
+        <v>99.07925762577139</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="B145" t="n">
-        <v>40.76224224931294</v>
+        <v>35.45332968915602</v>
       </c>
       <c r="C145" t="n">
-        <v>1.068987829575725</v>
+        <v>1.089944004760859</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -3913,22 +3913,22 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>97.18071177961139</v>
+        <v>99.08581861462356</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="B146" t="n">
-        <v>41.83011469306678</v>
+        <v>36.53058146010321</v>
       </c>
       <c r="C146" t="n">
-        <v>1.067872443753842</v>
+        <v>1.077251770947186</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -3937,22 +3937,22 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>97.07931306853109</v>
+        <v>97.93197917701687</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>93</v>
+        <v>37</v>
       </c>
       <c r="B147" t="n">
-        <v>42.89740927512767</v>
+        <v>37.60209236610033</v>
       </c>
       <c r="C147" t="n">
-        <v>1.067294582060889</v>
+        <v>1.071510905997123</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -3961,22 +3961,22 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>97.02678018735352</v>
+        <v>97.41008236337477</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="B148" t="n">
-        <v>43.96223453172722</v>
+        <v>38.67384202696605</v>
       </c>
       <c r="C148" t="n">
-        <v>1.064825256599548</v>
+        <v>1.07174966086572</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -3985,22 +3985,22 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>96.80229605450434</v>
+        <v>97.43178735142908</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="B149" t="n">
-        <v>45.02199540476474</v>
+        <v>39.74377372914694</v>
       </c>
       <c r="C149" t="n">
-        <v>1.059760873037519</v>
+        <v>1.069931702180888</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -4009,22 +4009,22 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>96.34189754886532</v>
+        <v>97.26651838008073</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="B150" t="n">
-        <v>46.08053865316903</v>
+        <v>40.81482844298118</v>
       </c>
       <c r="C150" t="n">
-        <v>1.058543248404291</v>
+        <v>1.071054713834243</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -4033,22 +4033,22 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>96.2312044003901</v>
+        <v>97.36861034856757</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="B151" t="n">
-        <v>47.13797982069934</v>
+        <v>41.89605911253297</v>
       </c>
       <c r="C151" t="n">
-        <v>1.057441167530314</v>
+        <v>1.081230669551793</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -4057,22 +4057,22 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>96.13101523002852</v>
+        <v>98.2936972319812</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="B152" t="n">
-        <v>1.153332504667897</v>
+        <v>42.97723465631597</v>
       </c>
       <c r="C152" t="n">
-        <v>1.153332504667897</v>
+        <v>1.081175543782997</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>CS2_37</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4081,22 +4081,22 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>104.8484095152634</v>
+        <v>98.2886857984543</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="B153" t="n">
-        <v>1.134444845802931</v>
+        <v>44.04587416026572</v>
       </c>
       <c r="C153" t="n">
-        <v>1.134444845802931</v>
+        <v>1.068639503949747</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>CS2_37</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4105,22 +4105,22 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>103.1313496184483</v>
+        <v>97.14904581361336</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="B154" t="n">
-        <v>1.133098066392579</v>
+        <v>45.11145101693138</v>
       </c>
       <c r="C154" t="n">
-        <v>1.133098066392579</v>
+        <v>1.065576856665658</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>CS2_37</t>
+          <t>CS2_38</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4129,18 +4129,18 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>103.0089151265981</v>
+        <v>96.8706233332416</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="B155" t="n">
-        <v>1.16241194625815</v>
+        <v>46.17707228063038</v>
       </c>
       <c r="C155" t="n">
-        <v>1.16241194625815</v>
+        <v>1.065621263699001</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -4153,18 +4153,18 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>105.6738132961954</v>
+        <v>96.87466033627277</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="B156" t="n">
-        <v>1.140773820517232</v>
+        <v>47.24233115472096</v>
       </c>
       <c r="C156" t="n">
-        <v>1.140773820517232</v>
+        <v>1.065258874090581</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -4177,18 +4177,18 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>103.706710956112</v>
+        <v>96.84171582641648</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="B157" t="n">
-        <v>1.139105930615482</v>
+        <v>48.30578414269559</v>
       </c>
       <c r="C157" t="n">
-        <v>1.139105930615482</v>
+        <v>1.063452987974628</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -4201,18 +4201,18 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>103.5550846014075</v>
+        <v>96.67754436132982</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B158" t="n">
-        <v>1.138543595376723</v>
+        <v>49.37966443932519</v>
       </c>
       <c r="C158" t="n">
-        <v>1.138543595376723</v>
+        <v>1.073880296629603</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -4225,18 +4225,18 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>103.5039632160657</v>
+        <v>97.62548151178213</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="B159" t="n">
-        <v>2.276498796615165</v>
+        <v>50.45417232904504</v>
       </c>
       <c r="C159" t="n">
-        <v>1.137955201238442</v>
+        <v>1.074507889719854</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -4249,18 +4249,18 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>103.4504728398584</v>
+        <v>97.68253542907762</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="B160" t="n">
-        <v>3.413179106350995</v>
+        <v>51.51861887799857</v>
       </c>
       <c r="C160" t="n">
-        <v>1.13668030973583</v>
+        <v>1.064446548953526</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -4273,18 +4273,18 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>103.3345736123482</v>
+        <v>96.76786808668422</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="B161" t="n">
-        <v>4.547398499644769</v>
+        <v>52.57995435510261</v>
       </c>
       <c r="C161" t="n">
-        <v>1.134219393293774</v>
+        <v>1.061335477104045</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -4297,18 +4297,18 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>103.1108539357977</v>
+        <v>96.48504337309498</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="B162" t="n">
-        <v>5.671115152841734</v>
+        <v>53.6398951031152</v>
       </c>
       <c r="C162" t="n">
-        <v>1.123716653196965</v>
+        <v>1.059940748012586</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -4321,18 +4321,18 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>102.1560593815423</v>
+        <v>96.35824981932602</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="B163" t="n">
-        <v>6.785802736033912</v>
+        <v>54.69869301159702</v>
       </c>
       <c r="C163" t="n">
-        <v>1.114687583192178</v>
+        <v>1.058797908481822</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -4345,1062 +4345,6 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>101.3352348356525</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>10</v>
-      </c>
-      <c r="B164" t="n">
-        <v>7.896140661276919</v>
-      </c>
-      <c r="C164" t="n">
-        <v>1.110337925243007</v>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F164" t="n">
-        <v>100.9398113857279</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
-        <v>11</v>
-      </c>
-      <c r="B165" t="n">
-        <v>9.003128063043921</v>
-      </c>
-      <c r="C165" t="n">
-        <v>1.106987401767001</v>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F165" t="n">
-        <v>100.6352183424546</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
-        <v>12</v>
-      </c>
-      <c r="B166" t="n">
-        <v>10.10719936217718</v>
-      </c>
-      <c r="C166" t="n">
-        <v>1.104071299133263</v>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F166" t="n">
-        <v>100.3701181030239</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
-        <v>13</v>
-      </c>
-      <c r="B167" t="n">
-        <v>11.21830930616636</v>
-      </c>
-      <c r="C167" t="n">
-        <v>1.111109943989181</v>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F167" t="n">
-        <v>101.0099949081074</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="n">
-        <v>14</v>
-      </c>
-      <c r="B168" t="n">
-        <v>12.33129184444021</v>
-      </c>
-      <c r="C168" t="n">
-        <v>1.112982538273844</v>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F168" t="n">
-        <v>101.1802307521676</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
-        <v>15</v>
-      </c>
-      <c r="B169" t="n">
-        <v>13.44429821496854</v>
-      </c>
-      <c r="C169" t="n">
-        <v>1.113006370528336</v>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F169" t="n">
-        <v>101.1823973207578</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>16</v>
-      </c>
-      <c r="B170" t="n">
-        <v>14.55696321107396</v>
-      </c>
-      <c r="C170" t="n">
-        <v>1.112664996105419</v>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F170" t="n">
-        <v>101.1513632823108</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>17</v>
-      </c>
-      <c r="B171" t="n">
-        <v>15.66905977805289</v>
-      </c>
-      <c r="C171" t="n">
-        <v>1.112096566978929</v>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F171" t="n">
-        <v>101.0996879071753</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>18</v>
-      </c>
-      <c r="B172" t="n">
-        <v>16.78078183103145</v>
-      </c>
-      <c r="C172" t="n">
-        <v>1.111722052978559</v>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F172" t="n">
-        <v>101.065641179869</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>19</v>
-      </c>
-      <c r="B173" t="n">
-        <v>17.8917186480297</v>
-      </c>
-      <c r="C173" t="n">
-        <v>1.110936816998251</v>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F173" t="n">
-        <v>100.9942560907501</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>20</v>
-      </c>
-      <c r="B174" t="n">
-        <v>19.00215402491973</v>
-      </c>
-      <c r="C174" t="n">
-        <v>1.110435376890031</v>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F174" t="n">
-        <v>100.9486706263665</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>21</v>
-      </c>
-      <c r="B175" t="n">
-        <v>20.11174053883676</v>
-      </c>
-      <c r="C175" t="n">
-        <v>1.10958651391703</v>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F175" t="n">
-        <v>100.8715012651845</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
-        <v>22</v>
-      </c>
-      <c r="B176" t="n">
-        <v>21.22055567953404</v>
-      </c>
-      <c r="C176" t="n">
-        <v>1.108815140697281</v>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F176" t="n">
-        <v>100.8013764270256</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
-        <v>23</v>
-      </c>
-      <c r="B177" t="n">
-        <v>22.32876013317005</v>
-      </c>
-      <c r="C177" t="n">
-        <v>1.108204453636006</v>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F177" t="n">
-        <v>100.7458594214551</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>24</v>
-      </c>
-      <c r="B178" t="n">
-        <v>23.43637941065311</v>
-      </c>
-      <c r="C178" t="n">
-        <v>1.10761927748306</v>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F178" t="n">
-        <v>100.6926615893691</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>25</v>
-      </c>
-      <c r="B179" t="n">
-        <v>24.54330866647413</v>
-      </c>
-      <c r="C179" t="n">
-        <v>1.106929255821022</v>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F179" t="n">
-        <v>100.6299323473656</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
-        <v>26</v>
-      </c>
-      <c r="B180" t="n">
-        <v>25.64969708119986</v>
-      </c>
-      <c r="C180" t="n">
-        <v>1.106388414725725</v>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F180" t="n">
-        <v>100.5807649750659</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
-        <v>27</v>
-      </c>
-      <c r="B181" t="n">
-        <v>26.75530855498607</v>
-      </c>
-      <c r="C181" t="n">
-        <v>1.105611473786208</v>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F181" t="n">
-        <v>100.5101339805644</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>28</v>
-      </c>
-      <c r="B182" t="n">
-        <v>27.8584226802503</v>
-      </c>
-      <c r="C182" t="n">
-        <v>1.103114125264234</v>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F182" t="n">
-        <v>100.2831022967486</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
-        <v>29</v>
-      </c>
-      <c r="B183" t="n">
-        <v>28.94836323080262</v>
-      </c>
-      <c r="C183" t="n">
-        <v>1.089940550552317</v>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F183" t="n">
-        <v>99.08550459566517</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>30</v>
-      </c>
-      <c r="B184" t="n">
-        <v>30.03335032605572</v>
-      </c>
-      <c r="C184" t="n">
-        <v>1.084987095253105</v>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F184" t="n">
-        <v>98.63519047755499</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>31</v>
-      </c>
-      <c r="B185" t="n">
-        <v>31.11533872147519</v>
-      </c>
-      <c r="C185" t="n">
-        <v>1.081988395419472</v>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F185" t="n">
-        <v>98.3625814017702</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>32</v>
-      </c>
-      <c r="B186" t="n">
-        <v>32.19464481784028</v>
-      </c>
-      <c r="C186" t="n">
-        <v>1.079306096365091</v>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F186" t="n">
-        <v>98.11873603319007</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>33</v>
-      </c>
-      <c r="B187" t="n">
-        <v>33.27351385051168</v>
-      </c>
-      <c r="C187" t="n">
-        <v>1.078869032671392</v>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F187" t="n">
-        <v>98.07900297012652</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>34</v>
-      </c>
-      <c r="B188" t="n">
-        <v>34.36338568439516</v>
-      </c>
-      <c r="C188" t="n">
-        <v>1.089871833883485</v>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F188" t="n">
-        <v>99.07925762577139</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>35</v>
-      </c>
-      <c r="B189" t="n">
-        <v>35.45332968915602</v>
-      </c>
-      <c r="C189" t="n">
-        <v>1.089944004760859</v>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F189" t="n">
-        <v>99.08581861462356</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>36</v>
-      </c>
-      <c r="B190" t="n">
-        <v>36.53058146010321</v>
-      </c>
-      <c r="C190" t="n">
-        <v>1.077251770947186</v>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F190" t="n">
-        <v>97.93197917701687</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>37</v>
-      </c>
-      <c r="B191" t="n">
-        <v>37.60209236610033</v>
-      </c>
-      <c r="C191" t="n">
-        <v>1.071510905997123</v>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F191" t="n">
-        <v>97.41008236337477</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>38</v>
-      </c>
-      <c r="B192" t="n">
-        <v>38.67384202696605</v>
-      </c>
-      <c r="C192" t="n">
-        <v>1.07174966086572</v>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F192" t="n">
-        <v>97.43178735142908</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>39</v>
-      </c>
-      <c r="B193" t="n">
-        <v>39.74377372914694</v>
-      </c>
-      <c r="C193" t="n">
-        <v>1.069931702180888</v>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F193" t="n">
-        <v>97.26651838008073</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>40</v>
-      </c>
-      <c r="B194" t="n">
-        <v>40.81482844298118</v>
-      </c>
-      <c r="C194" t="n">
-        <v>1.071054713834243</v>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F194" t="n">
-        <v>97.36861034856757</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>41</v>
-      </c>
-      <c r="B195" t="n">
-        <v>41.89605911253297</v>
-      </c>
-      <c r="C195" t="n">
-        <v>1.081230669551793</v>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F195" t="n">
-        <v>98.2936972319812</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>42</v>
-      </c>
-      <c r="B196" t="n">
-        <v>42.97723465631597</v>
-      </c>
-      <c r="C196" t="n">
-        <v>1.081175543782997</v>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F196" t="n">
-        <v>98.2886857984543</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>43</v>
-      </c>
-      <c r="B197" t="n">
-        <v>44.04587416026572</v>
-      </c>
-      <c r="C197" t="n">
-        <v>1.068639503949747</v>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F197" t="n">
-        <v>97.14904581361336</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>44</v>
-      </c>
-      <c r="B198" t="n">
-        <v>45.11145101693138</v>
-      </c>
-      <c r="C198" t="n">
-        <v>1.065576856665658</v>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F198" t="n">
-        <v>96.8706233332416</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>45</v>
-      </c>
-      <c r="B199" t="n">
-        <v>46.17707228063038</v>
-      </c>
-      <c r="C199" t="n">
-        <v>1.065621263699001</v>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F199" t="n">
-        <v>96.87466033627277</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>46</v>
-      </c>
-      <c r="B200" t="n">
-        <v>47.24233115472096</v>
-      </c>
-      <c r="C200" t="n">
-        <v>1.065258874090581</v>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F200" t="n">
-        <v>96.84171582641648</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>47</v>
-      </c>
-      <c r="B201" t="n">
-        <v>48.30578414269559</v>
-      </c>
-      <c r="C201" t="n">
-        <v>1.063452987974628</v>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F201" t="n">
-        <v>96.67754436132982</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="n">
-        <v>48</v>
-      </c>
-      <c r="B202" t="n">
-        <v>49.37966443932519</v>
-      </c>
-      <c r="C202" t="n">
-        <v>1.073880296629603</v>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F202" t="n">
-        <v>97.62548151178213</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
-        <v>49</v>
-      </c>
-      <c r="B203" t="n">
-        <v>50.45417232904504</v>
-      </c>
-      <c r="C203" t="n">
-        <v>1.074507889719854</v>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F203" t="n">
-        <v>97.68253542907762</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
-        <v>50</v>
-      </c>
-      <c r="B204" t="n">
-        <v>51.51861887799857</v>
-      </c>
-      <c r="C204" t="n">
-        <v>1.064446548953526</v>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F204" t="n">
-        <v>96.76786808668422</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="n">
-        <v>51</v>
-      </c>
-      <c r="B205" t="n">
-        <v>52.57995435510261</v>
-      </c>
-      <c r="C205" t="n">
-        <v>1.061335477104045</v>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F205" t="n">
-        <v>96.48504337309498</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="n">
-        <v>52</v>
-      </c>
-      <c r="B206" t="n">
-        <v>53.6398951031152</v>
-      </c>
-      <c r="C206" t="n">
-        <v>1.059940748012586</v>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F206" t="n">
-        <v>96.35824981932602</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="n">
-        <v>53</v>
-      </c>
-      <c r="B207" t="n">
-        <v>54.69869301159702</v>
-      </c>
-      <c r="C207" t="n">
-        <v>1.058797908481822</v>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>CS2_38</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F207" t="n">
         <v>96.25435531652923</v>
       </c>
     </row>

--- a/reports/Master_Retention_Summary.xlsx
+++ b/reports/Master_Retention_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F163"/>
+  <dimension ref="A1:F403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1734,17 +1734,17 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>1.160620725192767</v>
+        <v>1.052322023911945</v>
       </c>
       <c r="C55" t="n">
-        <v>1.160620725192767</v>
+        <v>1.052322023911945</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1753,22 +1753,22 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>105.5109750175243</v>
+        <v>95.66563853744955</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>1.145706012058183</v>
+        <v>2.149665492833128</v>
       </c>
       <c r="C56" t="n">
-        <v>1.145706012058183</v>
+        <v>1.097343468921183</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1777,22 +1777,22 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>104.1550920052894</v>
+        <v>99.75849717465297</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>1.144325684135661</v>
+        <v>3.245035743823332</v>
       </c>
       <c r="C57" t="n">
-        <v>1.144325684135661</v>
+        <v>1.095370250990204</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1801,22 +1801,22 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>104.0296076486964</v>
+        <v>99.57911372638219</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>1.14367469720064</v>
+        <v>4.3427396829912</v>
       </c>
       <c r="C58" t="n">
-        <v>1.14367469720064</v>
+        <v>1.097703939167868</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1825,22 +1825,22 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>103.97042701824</v>
+        <v>99.79126719707895</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>2.287056272080582</v>
+        <v>5.438155466960088</v>
       </c>
       <c r="C59" t="n">
-        <v>1.143381574879942</v>
+        <v>1.095415783968887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>103.9437795345402</v>
+        <v>99.58325308808065</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>3.427974174128568</v>
+        <v>6.408604373024617</v>
       </c>
       <c r="C60" t="n">
-        <v>1.140917902047986</v>
+        <v>0.9704489060645294</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>103.7198092770896</v>
+        <v>88.22262782404812</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>4.567072864414445</v>
+        <v>7.495652225355175</v>
       </c>
       <c r="C61" t="n">
-        <v>1.139098690285878</v>
+        <v>1.087047852330558</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1897,22 +1897,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>103.5544263896252</v>
+        <v>98.82253203005074</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>5.699412382971868</v>
+        <v>8.577396784697651</v>
       </c>
       <c r="C62" t="n">
-        <v>1.132339518557423</v>
+        <v>1.081744559342476</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>102.939956232493</v>
+        <v>98.34041448567962</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>6.824934965863919</v>
+        <v>9.654946259914045</v>
       </c>
       <c r="C63" t="n">
-        <v>1.125522582892051</v>
+        <v>1.077549475216394</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -1945,22 +1945,22 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>102.3202348083683</v>
+        <v>97.95904320149033</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>7.947224090755335</v>
+        <v>10.72613836450355</v>
       </c>
       <c r="C64" t="n">
-        <v>1.122289124891416</v>
+        <v>1.071192104589505</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -1969,22 +1969,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>102.0262840810378</v>
+        <v>97.38110041722771</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>9.066808359815637</v>
+        <v>11.79860684954863</v>
       </c>
       <c r="C65" t="n">
-        <v>1.119584269060302</v>
+        <v>1.072468485045077</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -1993,22 +1993,22 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>101.7803880963911</v>
+        <v>97.49713500409788</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>10.18430239488628</v>
+        <v>12.86786434001764</v>
       </c>
       <c r="C66" t="n">
-        <v>1.117494035070639</v>
+        <v>1.069257490469012</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2017,22 +2017,22 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>101.5903668246035</v>
+        <v>97.20522640627377</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>11.30616289495935</v>
+        <v>13.9297296638013</v>
       </c>
       <c r="C67" t="n">
-        <v>1.121860500073076</v>
+        <v>1.061865323783662</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2041,22 +2041,22 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>101.9873181884614</v>
+        <v>96.53321125306019</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>12.4288872660885</v>
+        <v>14.98952004353151</v>
       </c>
       <c r="C68" t="n">
-        <v>1.122724371129149</v>
+        <v>1.05979037973021</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2065,22 +2065,22 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>102.0658519208317</v>
+        <v>96.34457997547359</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>13.55142015898604</v>
+        <v>16.04749855873573</v>
       </c>
       <c r="C69" t="n">
-        <v>1.12253289289754</v>
+        <v>1.057978515204223</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2089,22 +2089,22 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>102.0484448088673</v>
+        <v>96.17986501856569</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>14.67373167987988</v>
+        <v>17.10340536937683</v>
       </c>
       <c r="C70" t="n">
-        <v>1.12231152089384</v>
+        <v>1.055906810641098</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2113,22 +2113,22 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>102.0283200812582</v>
+        <v>95.99152824009978</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>15.79553919430783</v>
+        <v>18.1556290521891</v>
       </c>
       <c r="C71" t="n">
-        <v>1.121807514427951</v>
+        <v>1.052223682812269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2137,22 +2137,22 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>101.9825013116319</v>
+        <v>95.65669843747897</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>16.91706944018753</v>
+        <v>19.20997154058639</v>
       </c>
       <c r="C72" t="n">
-        <v>1.121530245879701</v>
+        <v>1.054342488397296</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2161,22 +2161,22 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>101.9572950799728</v>
+        <v>95.84931712702691</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>18.03812130182694</v>
+        <v>20.26299732771692</v>
       </c>
       <c r="C73" t="n">
-        <v>1.121051861639405</v>
+        <v>1.053025787130522</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2185,22 +2185,22 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>101.9138056035822</v>
+        <v>95.72961701186567</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>19.15859188461094</v>
+        <v>21.31033341195971</v>
       </c>
       <c r="C74" t="n">
-        <v>1.120470582783998</v>
+        <v>1.047336084242794</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2209,22 +2209,22 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>101.8609620712725</v>
+        <v>95.21237129479941</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>20.27828101070494</v>
+        <v>22.35610598333428</v>
       </c>
       <c r="C75" t="n">
-        <v>1.119689126094002</v>
+        <v>1.045772571374567</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>101.7899205540002</v>
+        <v>95.07023376132425</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>21.39733029291349</v>
+        <v>23.40056677922347</v>
       </c>
       <c r="C76" t="n">
-        <v>1.119049282208554</v>
+        <v>1.044460795889197</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2257,22 +2257,22 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>101.7317529280503</v>
+        <v>94.95098144447246</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>22.51580588206711</v>
+        <v>24.44359582009594</v>
       </c>
       <c r="C77" t="n">
-        <v>1.118475589153618</v>
+        <v>1.043029040872465</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2281,22 +2281,22 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>101.6795990139653</v>
+        <v>94.82082189749683</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>23.63377103731687</v>
+        <v>25.4831948218273</v>
       </c>
       <c r="C78" t="n">
-        <v>1.117965155249763</v>
+        <v>1.039599001731357</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2305,22 +2305,22 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>101.6331959317966</v>
+        <v>94.5090001573961</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>24.75131912618462</v>
+        <v>26.52631445530069</v>
       </c>
       <c r="C79" t="n">
-        <v>1.11754808886775</v>
+        <v>1.043119633473388</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2329,22 +2329,22 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>101.5952808061591</v>
+        <v>94.82905758848985</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>25.86810255556341</v>
+        <v>27.5686670992941</v>
       </c>
       <c r="C80" t="n">
-        <v>1.116783429378792</v>
+        <v>1.042352643993418</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2353,22 +2353,22 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>101.5257663071629</v>
+        <v>94.75933127212889</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>26.98419280490191</v>
+        <v>28.60979222529076</v>
       </c>
       <c r="C81" t="n">
-        <v>1.116090249338491</v>
+        <v>1.041125125996658</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2377,22 +2377,22 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>101.4627499398628</v>
+        <v>94.64773872696887</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>28.09779683320157</v>
+        <v>29.64938541586051</v>
       </c>
       <c r="C82" t="n">
-        <v>1.113604028299665</v>
+        <v>1.03959319056975</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2401,22 +2401,22 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>101.2367298454241</v>
+        <v>94.50847186997728</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>29.20290224482232</v>
+        <v>30.68792447367722</v>
       </c>
       <c r="C83" t="n">
-        <v>1.105105411620745</v>
+        <v>1.038539057816706</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2425,22 +2425,22 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>100.4641283291586</v>
+        <v>94.41264161970055</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>30.30470221562137</v>
+        <v>31.7263162152612</v>
       </c>
       <c r="C84" t="n">
-        <v>1.101799970799057</v>
+        <v>1.038391741583983</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2449,22 +2449,22 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>100.1636337090052</v>
+        <v>94.39924923490749</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>31.40439926988345</v>
+        <v>32.76338812831584</v>
       </c>
       <c r="C85" t="n">
-        <v>1.099697054262073</v>
+        <v>1.037071913054639</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2473,22 +2473,22 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>99.97245947837027</v>
+        <v>94.27926482314901</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>32.50220020628813</v>
+        <v>33.7987298481729</v>
       </c>
       <c r="C86" t="n">
-        <v>1.097800936404685</v>
+        <v>1.035341719857065</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2497,22 +2497,22 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>99.80008512769861</v>
+        <v>94.12197453246048</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>33.60010431346337</v>
+        <v>34.83270037940027</v>
       </c>
       <c r="C87" t="n">
-        <v>1.097904107175239</v>
+        <v>1.033970531227368</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2521,22 +2521,22 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>99.80946428865809</v>
+        <v>93.9973210206698</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>34.70430089129693</v>
+        <v>35.86574666724295</v>
       </c>
       <c r="C88" t="n">
-        <v>1.104196577833562</v>
+        <v>1.033046287842673</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2545,22 +2545,22 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>100.3815070757784</v>
+        <v>93.91329889478844</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>35.80743829887539</v>
+        <v>36.89740618197521</v>
       </c>
       <c r="C89" t="n">
-        <v>1.103137407578458</v>
+        <v>1.031659514732269</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -2569,22 +2569,22 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>100.2852188707689</v>
+        <v>93.78722861202442</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>36.90275943419604</v>
+        <v>37.92829661484846</v>
       </c>
       <c r="C90" t="n">
-        <v>1.095321135320646</v>
+        <v>1.030890432873242</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2593,22 +2593,22 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>99.57464866551322</v>
+        <v>93.71731207938568</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>37.99494402981951</v>
+        <v>38.95850830029624</v>
       </c>
       <c r="C91" t="n">
-        <v>1.092184595623472</v>
+        <v>1.030211685447789</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -2617,22 +2617,22 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>99.28950869304289</v>
+        <v>93.65560776798078</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>39.08676575414849</v>
+        <v>39.98860228884588</v>
       </c>
       <c r="C92" t="n">
-        <v>1.09182172432898</v>
+        <v>1.030093988549631</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -2641,22 +2641,22 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>99.25652039354365</v>
+        <v>93.6449080499664</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>40.17728875732325</v>
+        <v>41.01705848167371</v>
       </c>
       <c r="C93" t="n">
-        <v>1.090523003174766</v>
+        <v>1.028456192827839</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -2665,22 +2665,22 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>99.13845483406966</v>
+        <v>93.49601752980357</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>41.26991966966544</v>
+        <v>42.04438475344786</v>
       </c>
       <c r="C94" t="n">
-        <v>1.092630912342187</v>
+        <v>1.027326271774143</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -2689,22 +2689,22 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>99.33008294019884</v>
+        <v>93.39329743401301</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>42.36777149253852</v>
+        <v>43.07010828743945</v>
       </c>
       <c r="C95" t="n">
-        <v>1.097851822873082</v>
+        <v>1.025723533991588</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -2713,22 +2713,22 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>99.80471117028019</v>
+        <v>93.24759399923526</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>43.46442817067955</v>
+        <v>44.08658300417674</v>
       </c>
       <c r="C96" t="n">
-        <v>1.096656678141024</v>
+        <v>1.016474716737292</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -2737,22 +2737,22 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>99.69606164918396</v>
+        <v>92.40679243066293</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>44.55312417120918</v>
+        <v>45.10024541836556</v>
       </c>
       <c r="C97" t="n">
-        <v>1.088696000529637</v>
+        <v>1.013662414188822</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -2761,22 +2761,22 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>98.97236368451247</v>
+        <v>92.15112856262017</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>45.6406334844156</v>
+        <v>46.1126554106551</v>
       </c>
       <c r="C98" t="n">
-        <v>1.087509313206418</v>
+        <v>1.012409992289541</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -2785,22 +2785,22 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>98.86448301876526</v>
+        <v>92.03727202632192</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>46.7276491070841</v>
+        <v>46.39238602108801</v>
       </c>
       <c r="C99" t="n">
-        <v>1.087015622668503</v>
+        <v>0.2797306104329067</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -2809,18 +2809,18 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>98.81960206077297</v>
+        <v>25.4300554939006</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="B100" t="n">
-        <v>47.81354911421985</v>
+        <v>1.160620725192767</v>
       </c>
       <c r="C100" t="n">
-        <v>1.085900007135749</v>
+        <v>1.160620725192767</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2833,18 +2833,18 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>98.71818246688622</v>
+        <v>105.5109750175243</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="B101" t="n">
-        <v>48.90022827517185</v>
+        <v>1.145706012058183</v>
       </c>
       <c r="C101" t="n">
-        <v>1.086679160951995</v>
+        <v>1.145706012058183</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2857,18 +2857,18 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>98.78901463199954</v>
+        <v>104.1550920052894</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B102" t="n">
-        <v>49.99289984994237</v>
+        <v>1.144325684135661</v>
       </c>
       <c r="C102" t="n">
-        <v>1.09267157477052</v>
+        <v>1.144325684135661</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -2881,18 +2881,18 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>99.33377952459274</v>
+        <v>104.0296076486964</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="B103" t="n">
-        <v>51.0848817033374</v>
+        <v>1.14367469720064</v>
       </c>
       <c r="C103" t="n">
-        <v>1.091981853395033</v>
+        <v>1.14367469720064</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -2905,18 +2905,18 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>99.27107758136667</v>
+        <v>103.97042701824</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="B104" t="n">
-        <v>52.17027203429442</v>
+        <v>2.287056272080582</v>
       </c>
       <c r="C104" t="n">
-        <v>1.085390330957019</v>
+        <v>1.143381574879942</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -2929,18 +2929,18 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>98.67184826881986</v>
+        <v>103.9437795345402</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="B105" t="n">
-        <v>53.25453964827329</v>
+        <v>3.427974174128568</v>
       </c>
       <c r="C105" t="n">
-        <v>1.084267613978867</v>
+        <v>1.140917902047986</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -2953,18 +2953,18 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>98.56978308898786</v>
+        <v>103.7198092770896</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="B106" t="n">
-        <v>54.33782742785704</v>
+        <v>4.567072864414445</v>
       </c>
       <c r="C106" t="n">
-        <v>1.083287779583756</v>
+        <v>1.139098690285878</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -2977,18 +2977,18 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>98.48070723488691</v>
+        <v>103.5544263896252</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="B107" t="n">
-        <v>55.41931950232025</v>
+        <v>5.699412382971868</v>
       </c>
       <c r="C107" t="n">
-        <v>1.081492074463206</v>
+        <v>1.132339518557423</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -3001,22 +3001,22 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>98.31746131483692</v>
+        <v>102.939956232493</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B108" t="n">
-        <v>1.153332504667897</v>
+        <v>6.824934965863919</v>
       </c>
       <c r="C108" t="n">
-        <v>1.153332504667897</v>
+        <v>1.125522582892051</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CS2_37</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3025,22 +3025,22 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>104.8484095152634</v>
+        <v>102.3202348083683</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B109" t="n">
-        <v>1.134444845802931</v>
+        <v>7.947224090755335</v>
       </c>
       <c r="C109" t="n">
-        <v>1.134444845802931</v>
+        <v>1.122289124891416</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>CS2_37</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3049,22 +3049,22 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>103.1313496184483</v>
+        <v>102.0262840810378</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B110" t="n">
-        <v>1.133098066392579</v>
+        <v>9.066808359815637</v>
       </c>
       <c r="C110" t="n">
-        <v>1.133098066392579</v>
+        <v>1.119584269060302</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>CS2_37</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3073,22 +3073,22 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>103.0089151265981</v>
+        <v>101.7803880963911</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B111" t="n">
-        <v>1.16241194625815</v>
+        <v>10.18430239488628</v>
       </c>
       <c r="C111" t="n">
-        <v>1.16241194625815</v>
+        <v>1.117494035070639</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3097,22 +3097,22 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>105.6738132961954</v>
+        <v>101.5903668246035</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B112" t="n">
-        <v>1.140773820517232</v>
+        <v>11.30616289495935</v>
       </c>
       <c r="C112" t="n">
-        <v>1.140773820517232</v>
+        <v>1.121860500073076</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -3121,22 +3121,22 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>103.706710956112</v>
+        <v>101.9873181884614</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B113" t="n">
-        <v>1.139105930615482</v>
+        <v>12.4288872660885</v>
       </c>
       <c r="C113" t="n">
-        <v>1.139105930615482</v>
+        <v>1.122724371129149</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3145,22 +3145,22 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>103.5550846014075</v>
+        <v>102.0658519208317</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B114" t="n">
-        <v>1.138543595376723</v>
+        <v>13.55142015898604</v>
       </c>
       <c r="C114" t="n">
-        <v>1.138543595376723</v>
+        <v>1.12253289289754</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -3169,22 +3169,22 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>103.5039632160657</v>
+        <v>102.0484448088673</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B115" t="n">
-        <v>2.276498796615165</v>
+        <v>14.67373167987988</v>
       </c>
       <c r="C115" t="n">
-        <v>1.137955201238442</v>
+        <v>1.12231152089384</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3193,22 +3193,22 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>103.4504728398584</v>
+        <v>102.0283200812582</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B116" t="n">
-        <v>3.413179106350995</v>
+        <v>15.79553919430783</v>
       </c>
       <c r="C116" t="n">
-        <v>1.13668030973583</v>
+        <v>1.121807514427951</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -3217,22 +3217,22 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>103.3345736123482</v>
+        <v>101.9825013116319</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B117" t="n">
-        <v>4.547398499644769</v>
+        <v>16.91706944018753</v>
       </c>
       <c r="C117" t="n">
-        <v>1.134219393293774</v>
+        <v>1.121530245879701</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -3241,22 +3241,22 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>103.1108539357977</v>
+        <v>101.9572950799728</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B118" t="n">
-        <v>5.671115152841734</v>
+        <v>18.03812130182694</v>
       </c>
       <c r="C118" t="n">
-        <v>1.123716653196965</v>
+        <v>1.121051861639405</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -3265,22 +3265,22 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>102.1560593815423</v>
+        <v>101.9138056035822</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B119" t="n">
-        <v>6.785802736033912</v>
+        <v>19.15859188461094</v>
       </c>
       <c r="C119" t="n">
-        <v>1.114687583192178</v>
+        <v>1.120470582783998</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -3289,22 +3289,22 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>101.3352348356525</v>
+        <v>101.8609620712725</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B120" t="n">
-        <v>7.896140661276919</v>
+        <v>20.27828101070494</v>
       </c>
       <c r="C120" t="n">
-        <v>1.110337925243007</v>
+        <v>1.119689126094002</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -3313,22 +3313,22 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>100.9398113857279</v>
+        <v>101.7899205540002</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B121" t="n">
-        <v>9.003128063043921</v>
+        <v>21.39733029291349</v>
       </c>
       <c r="C121" t="n">
-        <v>1.106987401767001</v>
+        <v>1.119049282208554</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -3337,22 +3337,22 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>100.6352183424546</v>
+        <v>101.7317529280503</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B122" t="n">
-        <v>10.10719936217718</v>
+        <v>22.51580588206711</v>
       </c>
       <c r="C122" t="n">
-        <v>1.104071299133263</v>
+        <v>1.118475589153618</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -3361,22 +3361,22 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>100.3701181030239</v>
+        <v>101.6795990139653</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B123" t="n">
-        <v>11.21830930616636</v>
+        <v>23.63377103731687</v>
       </c>
       <c r="C123" t="n">
-        <v>1.111109943989181</v>
+        <v>1.117965155249763</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -3385,22 +3385,22 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>101.0099949081074</v>
+        <v>101.6331959317966</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B124" t="n">
-        <v>12.33129184444021</v>
+        <v>24.75131912618462</v>
       </c>
       <c r="C124" t="n">
-        <v>1.112982538273844</v>
+        <v>1.11754808886775</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3409,22 +3409,22 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>101.1802307521676</v>
+        <v>101.5952808061591</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B125" t="n">
-        <v>13.44429821496854</v>
+        <v>25.86810255556341</v>
       </c>
       <c r="C125" t="n">
-        <v>1.113006370528336</v>
+        <v>1.116783429378792</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -3433,22 +3433,22 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>101.1823973207578</v>
+        <v>101.5257663071629</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B126" t="n">
-        <v>14.55696321107396</v>
+        <v>26.98419280490191</v>
       </c>
       <c r="C126" t="n">
-        <v>1.112664996105419</v>
+        <v>1.116090249338491</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -3457,22 +3457,22 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>101.1513632823108</v>
+        <v>101.4627499398628</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B127" t="n">
-        <v>15.66905977805289</v>
+        <v>28.09779683320157</v>
       </c>
       <c r="C127" t="n">
-        <v>1.112096566978929</v>
+        <v>1.113604028299665</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -3481,22 +3481,22 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>101.0996879071753</v>
+        <v>101.2367298454241</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B128" t="n">
-        <v>16.78078183103145</v>
+        <v>29.20290224482232</v>
       </c>
       <c r="C128" t="n">
-        <v>1.111722052978559</v>
+        <v>1.105105411620745</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -3505,22 +3505,22 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>101.065641179869</v>
+        <v>100.4641283291586</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B129" t="n">
-        <v>17.8917186480297</v>
+        <v>30.30470221562137</v>
       </c>
       <c r="C129" t="n">
-        <v>1.110936816998251</v>
+        <v>1.101799970799057</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -3529,22 +3529,22 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>100.9942560907501</v>
+        <v>100.1636337090052</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B130" t="n">
-        <v>19.00215402491973</v>
+        <v>31.40439926988345</v>
       </c>
       <c r="C130" t="n">
-        <v>1.110435376890031</v>
+        <v>1.099697054262073</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -3553,22 +3553,22 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>100.9486706263665</v>
+        <v>99.97245947837027</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B131" t="n">
-        <v>20.11174053883676</v>
+        <v>32.50220020628813</v>
       </c>
       <c r="C131" t="n">
-        <v>1.10958651391703</v>
+        <v>1.097800936404685</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -3577,22 +3577,22 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>100.8715012651845</v>
+        <v>99.80008512769861</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B132" t="n">
-        <v>21.22055567953404</v>
+        <v>33.60010431346337</v>
       </c>
       <c r="C132" t="n">
-        <v>1.108815140697281</v>
+        <v>1.097904107175239</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -3601,22 +3601,22 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>100.8013764270256</v>
+        <v>99.80946428865809</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B133" t="n">
-        <v>22.32876013317005</v>
+        <v>34.70430089129693</v>
       </c>
       <c r="C133" t="n">
-        <v>1.108204453636006</v>
+        <v>1.104196577833562</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -3625,22 +3625,22 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>100.7458594214551</v>
+        <v>100.3815070757784</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="B134" t="n">
-        <v>23.43637941065311</v>
+        <v>35.80743829887539</v>
       </c>
       <c r="C134" t="n">
-        <v>1.10761927748306</v>
+        <v>1.103137407578458</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -3649,22 +3649,22 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>100.6926615893691</v>
+        <v>100.2852188707689</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B135" t="n">
-        <v>24.54330866647413</v>
+        <v>36.90275943419604</v>
       </c>
       <c r="C135" t="n">
-        <v>1.106929255821022</v>
+        <v>1.095321135320646</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -3673,22 +3673,22 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>100.6299323473656</v>
+        <v>99.57464866551322</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B136" t="n">
-        <v>25.64969708119986</v>
+        <v>37.99494402981951</v>
       </c>
       <c r="C136" t="n">
-        <v>1.106388414725725</v>
+        <v>1.092184595623472</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -3697,22 +3697,22 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>100.5807649750659</v>
+        <v>99.28950869304289</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B137" t="n">
-        <v>26.75530855498607</v>
+        <v>39.08676575414849</v>
       </c>
       <c r="C137" t="n">
-        <v>1.105611473786208</v>
+        <v>1.09182172432898</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -3721,22 +3721,22 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>100.5101339805644</v>
+        <v>99.25652039354365</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B138" t="n">
-        <v>27.8584226802503</v>
+        <v>40.17728875732325</v>
       </c>
       <c r="C138" t="n">
-        <v>1.103114125264234</v>
+        <v>1.090523003174766</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -3745,22 +3745,22 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>100.2831022967486</v>
+        <v>99.13845483406966</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B139" t="n">
-        <v>28.94836323080262</v>
+        <v>41.26991966966544</v>
       </c>
       <c r="C139" t="n">
-        <v>1.089940550552317</v>
+        <v>1.092630912342187</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -3769,22 +3769,22 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>99.08550459566517</v>
+        <v>99.33008294019884</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B140" t="n">
-        <v>30.03335032605572</v>
+        <v>42.36777149253852</v>
       </c>
       <c r="C140" t="n">
-        <v>1.084987095253105</v>
+        <v>1.097851822873082</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -3793,22 +3793,22 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>98.63519047755499</v>
+        <v>99.80471117028019</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B141" t="n">
-        <v>31.11533872147519</v>
+        <v>43.46442817067955</v>
       </c>
       <c r="C141" t="n">
-        <v>1.081988395419472</v>
+        <v>1.096656678141024</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -3817,22 +3817,22 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>98.3625814017702</v>
+        <v>99.69606164918396</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="B142" t="n">
-        <v>32.19464481784028</v>
+        <v>44.55312417120918</v>
       </c>
       <c r="C142" t="n">
-        <v>1.079306096365091</v>
+        <v>1.088696000529637</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -3841,22 +3841,22 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>98.11873603319007</v>
+        <v>98.97236368451247</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B143" t="n">
-        <v>33.27351385051168</v>
+        <v>45.6406334844156</v>
       </c>
       <c r="C143" t="n">
-        <v>1.078869032671392</v>
+        <v>1.087509313206418</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -3865,22 +3865,22 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>98.07900297012652</v>
+        <v>98.86448301876526</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B144" t="n">
-        <v>34.36338568439516</v>
+        <v>46.7276491070841</v>
       </c>
       <c r="C144" t="n">
-        <v>1.089871833883485</v>
+        <v>1.087015622668503</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -3889,22 +3889,22 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>99.07925762577139</v>
+        <v>98.81960206077297</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B145" t="n">
-        <v>35.45332968915602</v>
+        <v>47.81354911421985</v>
       </c>
       <c r="C145" t="n">
-        <v>1.089944004760859</v>
+        <v>1.085900007135749</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -3913,22 +3913,22 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>99.08581861462356</v>
+        <v>98.71818246688622</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B146" t="n">
-        <v>36.53058146010321</v>
+        <v>48.90022827517185</v>
       </c>
       <c r="C146" t="n">
-        <v>1.077251770947186</v>
+        <v>1.086679160951995</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -3937,22 +3937,22 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>97.93197917701687</v>
+        <v>98.78901463199954</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B147" t="n">
-        <v>37.60209236610033</v>
+        <v>49.99289984994237</v>
       </c>
       <c r="C147" t="n">
-        <v>1.071510905997123</v>
+        <v>1.09267157477052</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -3961,22 +3961,22 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>97.41008236337477</v>
+        <v>99.33377952459274</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B148" t="n">
-        <v>38.67384202696605</v>
+        <v>51.0848817033374</v>
       </c>
       <c r="C148" t="n">
-        <v>1.07174966086572</v>
+        <v>1.091981853395033</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -3985,22 +3985,22 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>97.43178735142908</v>
+        <v>99.27107758136667</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B149" t="n">
-        <v>39.74377372914694</v>
+        <v>52.17027203429442</v>
       </c>
       <c r="C149" t="n">
-        <v>1.069931702180888</v>
+        <v>1.085390330957019</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -4009,22 +4009,22 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>97.26651838008073</v>
+        <v>98.67184826881986</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B150" t="n">
-        <v>40.81482844298118</v>
+        <v>53.25453964827329</v>
       </c>
       <c r="C150" t="n">
-        <v>1.071054713834243</v>
+        <v>1.084267613978867</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -4033,22 +4033,22 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>97.36861034856757</v>
+        <v>98.56978308898786</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B151" t="n">
-        <v>41.89605911253297</v>
+        <v>54.33782742785704</v>
       </c>
       <c r="C151" t="n">
-        <v>1.081230669551793</v>
+        <v>1.083287779583756</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -4057,22 +4057,22 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>98.2936972319812</v>
+        <v>98.48070723488691</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B152" t="n">
-        <v>42.97723465631597</v>
+        <v>55.41931950232025</v>
       </c>
       <c r="C152" t="n">
-        <v>1.081175543782997</v>
+        <v>1.081492074463206</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4081,22 +4081,22 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>98.2886857984543</v>
+        <v>98.31746131483692</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B153" t="n">
-        <v>44.04587416026572</v>
+        <v>0.113111490685807</v>
       </c>
       <c r="C153" t="n">
-        <v>1.068639503949747</v>
+        <v>0.113111490685807</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4105,22 +4105,22 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>97.14904581361336</v>
+        <v>10.28286278961882</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B154" t="n">
-        <v>45.11145101693138</v>
+        <v>1.178657625988216</v>
       </c>
       <c r="C154" t="n">
-        <v>1.065576856665658</v>
+        <v>1.065546135302409</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4129,22 +4129,22 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>96.8706233332416</v>
+        <v>96.86783048203716</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B155" t="n">
-        <v>46.17707228063038</v>
+        <v>2.243739205538597</v>
       </c>
       <c r="C155" t="n">
-        <v>1.065621263699001</v>
+        <v>1.065081579550381</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -4153,22 +4153,22 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>96.87466033627277</v>
+        <v>96.82559814094371</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B156" t="n">
-        <v>47.24233115472096</v>
+        <v>3.309092688315239</v>
       </c>
       <c r="C156" t="n">
-        <v>1.065258874090581</v>
+        <v>1.065353482776642</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4177,22 +4177,22 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>96.84171582641648</v>
+        <v>96.85031661605838</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B157" t="n">
-        <v>48.30578414269559</v>
+        <v>4.378780629518028</v>
       </c>
       <c r="C157" t="n">
-        <v>1.063452987974628</v>
+        <v>1.069687941202789</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -4201,22 +4201,22 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>96.67754436132982</v>
+        <v>97.2443582911626</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B158" t="n">
-        <v>49.37966443932519</v>
+        <v>5.448628276990655</v>
       </c>
       <c r="C158" t="n">
-        <v>1.073880296629603</v>
+        <v>1.069847647472627</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -4225,22 +4225,22 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>97.62548151178213</v>
+        <v>97.25887704296606</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B159" t="n">
-        <v>50.45417232904504</v>
+        <v>6.512756992194999</v>
       </c>
       <c r="C159" t="n">
-        <v>1.074507889719854</v>
+        <v>1.064128715204344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>97.68253542907762</v>
+        <v>96.73897410948581</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B160" t="n">
-        <v>51.51861887799857</v>
+        <v>7.575420156200408</v>
       </c>
       <c r="C160" t="n">
-        <v>1.064446548953526</v>
+        <v>1.06266316400541</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -4273,22 +4273,22 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>96.76786808668422</v>
+        <v>96.60574218230997</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B161" t="n">
-        <v>52.57995435510261</v>
+        <v>8.637442958524062</v>
       </c>
       <c r="C161" t="n">
-        <v>1.061335477104045</v>
+        <v>1.062022802323654</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>96.48504337309498</v>
+        <v>96.54752748396849</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B162" t="n">
-        <v>53.6398951031152</v>
+        <v>9.698265864921773</v>
       </c>
       <c r="C162" t="n">
-        <v>1.059940748012586</v>
+        <v>1.060822906397711</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -4321,30 +4321,5790 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>96.35824981932602</v>
+        <v>96.4384460361555</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
+        <v>64</v>
+      </c>
+      <c r="B163" t="n">
+        <v>10.75840713420893</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1.060141269287156</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>96.37647902610507</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>65</v>
+      </c>
+      <c r="B164" t="n">
+        <v>11.82398030303404</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1.065573168825116</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>96.87028807501056</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>66</v>
+      </c>
+      <c r="B165" t="n">
+        <v>12.77680908399321</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0.9528287809591696</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>86.62079826901541</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>67</v>
+      </c>
+      <c r="B166" t="n">
+        <v>13.84242658350831</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1.065617499515097</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>96.87431813773611</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>68</v>
+      </c>
+      <c r="B167" t="n">
+        <v>14.89964252579231</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1.057215942283996</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>96.11054020763599</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>69</v>
+      </c>
+      <c r="B168" t="n">
+        <v>15.9568513015529</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1.057208775760589</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>96.10988870550811</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>70</v>
+      </c>
+      <c r="B169" t="n">
+        <v>17.01333994783467</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1.056488646281773</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>96.04442238925208</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>71</v>
+      </c>
+      <c r="B170" t="n">
+        <v>18.06701076120776</v>
+      </c>
+      <c r="C170" t="n">
+        <v>1.053670813373092</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>95.78825576119017</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>72</v>
+      </c>
+      <c r="B171" t="n">
+        <v>19.12636525092073</v>
+      </c>
+      <c r="C171" t="n">
+        <v>1.05935448971297</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>96.30495361026996</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>73</v>
+      </c>
+      <c r="B172" t="n">
+        <v>20.07319640184689</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0.9468311509261582</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>86.07555917510528</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>74</v>
+      </c>
+      <c r="B173" t="n">
+        <v>21.13603989920749</v>
+      </c>
+      <c r="C173" t="n">
+        <v>1.062843497360603</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>96.62213612369121</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>75</v>
+      </c>
+      <c r="B174" t="n">
+        <v>22.18899019985422</v>
+      </c>
+      <c r="C174" t="n">
+        <v>1.052950300646732</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>95.72275460424832</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>76</v>
+      </c>
+      <c r="B175" t="n">
+        <v>23.24130698959751</v>
+      </c>
+      <c r="C175" t="n">
+        <v>1.052316789743283</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>95.66516270393485</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>77</v>
+      </c>
+      <c r="B176" t="n">
+        <v>24.29375318093989</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1.05244619134238</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>95.6769264856709</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>78</v>
+      </c>
+      <c r="B177" t="n">
+        <v>25.3438624591865</v>
+      </c>
+      <c r="C177" t="n">
+        <v>1.050109278246609</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>95.46447984060079</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>79</v>
+      </c>
+      <c r="B178" t="n">
+        <v>26.39459459187542</v>
+      </c>
+      <c r="C178" t="n">
+        <v>1.050732132688925</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>95.52110297172042</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>80</v>
+      </c>
+      <c r="B179" t="n">
+        <v>27.45201801113362</v>
+      </c>
+      <c r="C179" t="n">
+        <v>1.057423419258196</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>96.1294017507451</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>81</v>
+      </c>
+      <c r="B180" t="n">
+        <v>28.51040877664675</v>
+      </c>
+      <c r="C180" t="n">
+        <v>1.058390765513135</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>96.21734231937589</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>82</v>
+      </c>
+      <c r="B181" t="n">
+        <v>29.57045325510635</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1.060044478459595</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>96.36767985996318</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>83</v>
+      </c>
+      <c r="B182" t="n">
+        <v>30.63152953715822</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1.061076282051875</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>96.46148018653409</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>84</v>
+      </c>
+      <c r="B183" t="n">
+        <v>31.69328537017217</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1.061755833013947</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>96.52325754672249</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>85</v>
+      </c>
+      <c r="B184" t="n">
+        <v>32.7556362546977</v>
+      </c>
+      <c r="C184" t="n">
+        <v>1.062350884525529</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>96.57735313868442</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>86</v>
+      </c>
+      <c r="B185" t="n">
+        <v>33.81846422965042</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1.062827974952725</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>96.62072499570228</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>87</v>
+      </c>
+      <c r="B186" t="n">
+        <v>34.88187073694125</v>
+      </c>
+      <c r="C186" t="n">
+        <v>1.063406507290821</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>96.67331884462013</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>88</v>
+      </c>
+      <c r="B187" t="n">
+        <v>35.94532355992024</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1.063452822978995</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>96.67752936172681</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>89</v>
+      </c>
+      <c r="B188" t="n">
+        <v>37.00902599630624</v>
+      </c>
+      <c r="C188" t="n">
+        <v>1.063702436386002</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>96.70022148963655</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>90</v>
+      </c>
+      <c r="B189" t="n">
+        <v>38.07289984427906</v>
+      </c>
+      <c r="C189" t="n">
+        <v>1.063873847972822</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>96.71580436116561</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>91</v>
+      </c>
+      <c r="B190" t="n">
+        <v>39.13685033867657</v>
+      </c>
+      <c r="C190" t="n">
+        <v>1.063950494397503</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>96.72277221795478</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>92</v>
+      </c>
+      <c r="B191" t="n">
+        <v>40.20092532006711</v>
+      </c>
+      <c r="C191" t="n">
+        <v>1.06407498139054</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>96.73408921732182</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>93</v>
+      </c>
+      <c r="B192" t="n">
+        <v>41.26509702875236</v>
+      </c>
+      <c r="C192" t="n">
+        <v>1.064171708685251</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>96.74288260775008</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>94</v>
+      </c>
+      <c r="B193" t="n">
+        <v>42.32921691123793</v>
+      </c>
+      <c r="C193" t="n">
+        <v>1.064119882485571</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>96.73817113505187</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>95</v>
+      </c>
+      <c r="B194" t="n">
+        <v>43.39327611779943</v>
+      </c>
+      <c r="C194" t="n">
+        <v>1.064059206561502</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>96.73265514195477</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>96</v>
+      </c>
+      <c r="B195" t="n">
+        <v>44.44763541374989</v>
+      </c>
+      <c r="C195" t="n">
+        <v>1.054359295950455</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>95.850845086405</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>97</v>
+      </c>
+      <c r="B196" t="n">
+        <v>45.49802847784131</v>
+      </c>
+      <c r="C196" t="n">
+        <v>1.050393064091423</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>95.49027855376576</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>98</v>
+      </c>
+      <c r="B197" t="n">
+        <v>46.54790759052996</v>
+      </c>
+      <c r="C197" t="n">
+        <v>1.04987911268865</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>95.4435556989682</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>99</v>
+      </c>
+      <c r="B198" t="n">
+        <v>47.59697903732324</v>
+      </c>
+      <c r="C198" t="n">
+        <v>1.049071446793278</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>95.37013152666159</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>100</v>
+      </c>
+      <c r="B199" t="n">
+        <v>48.64531910116042</v>
+      </c>
+      <c r="C199" t="n">
+        <v>1.04834006383718</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>95.30364216701641</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>101</v>
+      </c>
+      <c r="B200" t="n">
+        <v>49.70065970302701</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1.055340601866597</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>95.94005471514515</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>102</v>
+      </c>
+      <c r="B201" t="n">
+        <v>50.75792044099337</v>
+      </c>
+      <c r="C201" t="n">
+        <v>1.057260737966359</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>96.1146125423963</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>103</v>
+      </c>
+      <c r="B202" t="n">
+        <v>51.80996396286784</v>
+      </c>
+      <c r="C202" t="n">
+        <v>1.052043521874467</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>95.64032017040604</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>1</v>
+      </c>
+      <c r="B203" t="n">
+        <v>1.153332504667897</v>
+      </c>
+      <c r="C203" t="n">
+        <v>1.153332504667897</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>104.8484095152634</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>2</v>
+      </c>
+      <c r="B204" t="n">
+        <v>1.134444845802931</v>
+      </c>
+      <c r="C204" t="n">
+        <v>1.134444845802931</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>103.1313496184483</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>3</v>
+      </c>
+      <c r="B205" t="n">
+        <v>1.133098066392579</v>
+      </c>
+      <c r="C205" t="n">
+        <v>1.133098066392579</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>103.0089151265981</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>4</v>
+      </c>
+      <c r="B206" t="n">
+        <v>1.132467222574529</v>
+      </c>
+      <c r="C206" t="n">
+        <v>1.132467222574529</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>102.9515656885935</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>5</v>
+      </c>
+      <c r="B207" t="n">
+        <v>2.264728143988592</v>
+      </c>
+      <c r="C207" t="n">
+        <v>1.132260921414063</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>102.9328110376421</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>6</v>
+      </c>
+      <c r="B208" t="n">
+        <v>3.394346187884022</v>
+      </c>
+      <c r="C208" t="n">
+        <v>1.12961804389543</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>102.6925494450391</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>7</v>
+      </c>
+      <c r="B209" t="n">
+        <v>4.521569338404709</v>
+      </c>
+      <c r="C209" t="n">
+        <v>1.127223150520687</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>102.474831865517</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>8</v>
+      </c>
+      <c r="B210" t="n">
+        <v>5.639199174651068</v>
+      </c>
+      <c r="C210" t="n">
+        <v>1.117629836246359</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>101.6027123860326</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>9</v>
+      </c>
+      <c r="B211" t="n">
+        <v>6.747363160034188</v>
+      </c>
+      <c r="C211" t="n">
+        <v>1.108163985383119</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>100.7421804893745</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>10</v>
+      </c>
+      <c r="B212" t="n">
+        <v>7.851289062493303</v>
+      </c>
+      <c r="C212" t="n">
+        <v>1.103925902459116</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>100.356900223556</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>11</v>
+      </c>
+      <c r="B213" t="n">
+        <v>8.951853853384192</v>
+      </c>
+      <c r="C213" t="n">
+        <v>1.100564790890888</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>100.0513446264444</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>12</v>
+      </c>
+      <c r="B214" t="n">
+        <v>10.04963413816988</v>
+      </c>
+      <c r="C214" t="n">
+        <v>1.097780284785689</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>99.79820770778987</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>13</v>
+      </c>
+      <c r="B215" t="n">
+        <v>11.15380548303818</v>
+      </c>
+      <c r="C215" t="n">
+        <v>1.1041713448683</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>100.3792131698455</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>14</v>
+      </c>
+      <c r="B216" t="n">
+        <v>12.25949224697698</v>
+      </c>
+      <c r="C216" t="n">
+        <v>1.105686763938804</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>100.5169785398913</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>15</v>
+      </c>
+      <c r="B217" t="n">
+        <v>13.36524239534484</v>
+      </c>
+      <c r="C217" t="n">
+        <v>1.105750148367857</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>100.5227407607143</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>16</v>
+      </c>
+      <c r="B218" t="n">
+        <v>14.47070333154756</v>
+      </c>
+      <c r="C218" t="n">
+        <v>1.105460936202718</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>100.4964487457016</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>17</v>
+      </c>
+      <c r="B219" t="n">
+        <v>15.46730046483489</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0.9965971332873291</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>90.59973938975719</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>18</v>
+      </c>
+      <c r="B220" t="n">
+        <v>16.57437878034292</v>
+      </c>
+      <c r="C220" t="n">
+        <v>1.107078315508033</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>100.643483228003</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>19</v>
+      </c>
+      <c r="B221" t="n">
+        <v>17.67861301870839</v>
+      </c>
+      <c r="C221" t="n">
+        <v>1.104234238365471</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>100.3849307604974</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>20</v>
+      </c>
+      <c r="B222" t="n">
+        <v>18.78221884376025</v>
+      </c>
+      <c r="C222" t="n">
+        <v>1.103605825051858</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>100.3278022774416</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>21</v>
+      </c>
+      <c r="B223" t="n">
+        <v>19.88505740386118</v>
+      </c>
+      <c r="C223" t="n">
+        <v>1.102838560100931</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>100.2580509182665</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>22</v>
+      </c>
+      <c r="B224" t="n">
+        <v>20.98715406262716</v>
+      </c>
+      <c r="C224" t="n">
+        <v>1.102096658765973</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>100.1906053423612</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>23</v>
+      </c>
+      <c r="B225" t="n">
+        <v>22.08862904974963</v>
+      </c>
+      <c r="C225" t="n">
+        <v>1.101474987122476</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>100.1340897384069</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>24</v>
+      </c>
+      <c r="B226" t="n">
+        <v>23.18950370664525</v>
+      </c>
+      <c r="C226" t="n">
+        <v>1.100874656895616</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>100.0795142632378</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>25</v>
+      </c>
+      <c r="B227" t="n">
+        <v>24.28987560103025</v>
+      </c>
+      <c r="C227" t="n">
+        <v>1.100371894385002</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>100.0338085804548</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>26</v>
+      </c>
+      <c r="B228" t="n">
+        <v>25.38966866099365</v>
+      </c>
+      <c r="C228" t="n">
+        <v>1.0997930599634</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>99.98118726939995</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>27</v>
+      </c>
+      <c r="B229" t="n">
+        <v>26.48873465519709</v>
+      </c>
+      <c r="C229" t="n">
+        <v>1.099065994203439</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>99.91509038213083</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>28</v>
+      </c>
+      <c r="B230" t="n">
+        <v>27.58701313139907</v>
+      </c>
+      <c r="C230" t="n">
+        <v>1.09827847620198</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>99.84349783654361</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>29</v>
+      </c>
+      <c r="B231" t="n">
+        <v>28.67563752673422</v>
+      </c>
+      <c r="C231" t="n">
+        <v>1.088624395335149</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>98.96585412137716</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>30</v>
+      </c>
+      <c r="B232" t="n">
+        <v>29.75530964113399</v>
+      </c>
+      <c r="C232" t="n">
+        <v>1.079672114399774</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>98.15201039997942</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>31</v>
+      </c>
+      <c r="B233" t="n">
+        <v>30.83146273693261</v>
+      </c>
+      <c r="C233" t="n">
+        <v>1.07615309579862</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>97.83209961805638</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>32</v>
+      </c>
+      <c r="B234" t="n">
+        <v>31.90514906362365</v>
+      </c>
+      <c r="C234" t="n">
+        <v>1.073686326691039</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>97.60784788100354</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>33</v>
+      </c>
+      <c r="B235" t="n">
+        <v>32.97711423228421</v>
+      </c>
+      <c r="C235" t="n">
+        <v>1.071965168660558</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>97.45137896914163</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>34</v>
+      </c>
+      <c r="B236" t="n">
+        <v>34.05857040457042</v>
+      </c>
+      <c r="C236" t="n">
+        <v>1.081456172286217</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>98.31419748056514</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>35</v>
+      </c>
+      <c r="B237" t="n">
+        <v>35.14276510493571</v>
+      </c>
+      <c r="C237" t="n">
+        <v>1.084194700365281</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>98.56315457866187</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>36</v>
+      </c>
+      <c r="B238" t="n">
+        <v>36.22053461150617</v>
+      </c>
+      <c r="C238" t="n">
+        <v>1.077769506570462</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>97.97904605186018</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>37</v>
+      </c>
+      <c r="B239" t="n">
+        <v>37.28913093339772</v>
+      </c>
+      <c r="C239" t="n">
+        <v>1.068596321891555</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>97.1451201719595</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>38</v>
+      </c>
+      <c r="B240" t="n">
+        <v>38.35479300584866</v>
+      </c>
+      <c r="C240" t="n">
+        <v>1.065662072450934</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>96.87837022281217</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>39</v>
+      </c>
+      <c r="B241" t="n">
+        <v>39.41927832094845</v>
+      </c>
+      <c r="C241" t="n">
+        <v>1.064485315099795</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>96.77139228179951</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>40</v>
+      </c>
+      <c r="B242" t="n">
+        <v>40.48248629667058</v>
+      </c>
+      <c r="C242" t="n">
+        <v>1.063207975722129</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>96.65527052019355</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>41</v>
+      </c>
+      <c r="B243" t="n">
+        <v>41.55590687473016</v>
+      </c>
+      <c r="C243" t="n">
+        <v>1.073420578059576</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>97.58368891450688</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>42</v>
+      </c>
+      <c r="B244" t="n">
+        <v>42.6316702283717</v>
+      </c>
+      <c r="C244" t="n">
+        <v>1.075763353641541</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>97.79666851286737</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>43</v>
+      </c>
+      <c r="B245" t="n">
+        <v>43.70501132714502</v>
+      </c>
+      <c r="C245" t="n">
+        <v>1.073341098773327</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>97.57646352484785</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>44</v>
+      </c>
+      <c r="B246" t="n">
+        <v>44.76579317159603</v>
+      </c>
+      <c r="C246" t="n">
+        <v>1.060781844451007</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>96.43471313190975</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>45</v>
+      </c>
+      <c r="B247" t="n">
+        <v>45.82571542167062</v>
+      </c>
+      <c r="C247" t="n">
+        <v>1.059922250074592</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>96.3565681885993</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>46</v>
+      </c>
+      <c r="B248" t="n">
+        <v>46.88409740877964</v>
+      </c>
+      <c r="C248" t="n">
+        <v>1.058381987109016</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>96.21654428263778</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>47</v>
+      </c>
+      <c r="B249" t="n">
+        <v>47.94057152340084</v>
+      </c>
+      <c r="C249" t="n">
+        <v>1.056474114621203</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>96.04310132920025</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>48</v>
+      </c>
+      <c r="B250" t="n">
+        <v>49.00432391362465</v>
+      </c>
+      <c r="C250" t="n">
+        <v>1.063752390223804</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>96.70476274761857</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>49</v>
+      </c>
+      <c r="B251" t="n">
+        <v>50.07254596194111</v>
+      </c>
+      <c r="C251" t="n">
+        <v>1.068222048316464</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>97.11109530149673</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>50</v>
+      </c>
+      <c r="B252" t="n">
+        <v>51.13986054730108</v>
+      </c>
+      <c r="C252" t="n">
+        <v>1.067314585359973</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>97.0285986690885</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>51</v>
+      </c>
+      <c r="B253" t="n">
+        <v>52.19600464114075</v>
+      </c>
+      <c r="C253" t="n">
+        <v>1.056144093839663</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>96.01309943996935</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>52</v>
+      </c>
+      <c r="B254" t="n">
+        <v>53.25070269288215</v>
+      </c>
+      <c r="C254" t="n">
+        <v>1.054698051741404</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>95.88164106740037</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
         <v>53</v>
       </c>
-      <c r="B163" t="n">
+      <c r="B255" t="n">
+        <v>54.30402234212134</v>
+      </c>
+      <c r="C255" t="n">
+        <v>1.053319649239192</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>95.75633174901748</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>54</v>
+      </c>
+      <c r="B256" t="n">
+        <v>0.07563219140932</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0.07563219140932</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>6.875653764483635</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>55</v>
+      </c>
+      <c r="B257" t="n">
+        <v>1.110850740685462</v>
+      </c>
+      <c r="C257" t="n">
+        <v>1.035218549276142</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>94.11077720692198</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>56</v>
+      </c>
+      <c r="B258" t="n">
+        <v>2.144961806335799</v>
+      </c>
+      <c r="C258" t="n">
+        <v>1.034111065650337</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>94.01009687730335</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>57</v>
+      </c>
+      <c r="B259" t="n">
+        <v>3.178725482593916</v>
+      </c>
+      <c r="C259" t="n">
+        <v>1.033763676258117</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F259" t="n">
+        <v>93.97851602346518</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>58</v>
+      </c>
+      <c r="B260" t="n">
+        <v>4.21837887910829</v>
+      </c>
+      <c r="C260" t="n">
+        <v>1.039653396514374</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>94.51394513767033</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>59</v>
+      </c>
+      <c r="B261" t="n">
+        <v>5.25905431909567</v>
+      </c>
+      <c r="C261" t="n">
+        <v>1.04067543998738</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>94.60685818067091</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>60</v>
+      </c>
+      <c r="B262" t="n">
+        <v>6.292132751401832</v>
+      </c>
+      <c r="C262" t="n">
+        <v>1.033078432306162</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>93.916221118742</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>61</v>
+      </c>
+      <c r="B263" t="n">
+        <v>7.320993590810906</v>
+      </c>
+      <c r="C263" t="n">
+        <v>1.028860839409074</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>93.53280358264306</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>62</v>
+      </c>
+      <c r="B264" t="n">
+        <v>8.349735176017591</v>
+      </c>
+      <c r="C264" t="n">
+        <v>1.028741585206685</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
+        <v>93.52196229151681</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>63</v>
+      </c>
+      <c r="B265" t="n">
+        <v>9.376901656900538</v>
+      </c>
+      <c r="C265" t="n">
+        <v>1.027166480882947</v>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>93.37877098935881</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>64</v>
+      </c>
+      <c r="B266" t="n">
+        <v>10.402141297363</v>
+      </c>
+      <c r="C266" t="n">
+        <v>1.025239640462459</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>93.20360367840537</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>65</v>
+      </c>
+      <c r="B267" t="n">
+        <v>11.43451266915411</v>
+      </c>
+      <c r="C267" t="n">
+        <v>1.032371371791111</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>93.851942890101</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>66</v>
+      </c>
+      <c r="B268" t="n">
+        <v>12.4686617579132</v>
+      </c>
+      <c r="C268" t="n">
+        <v>1.034149088759092</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>94.0135535235538</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>67</v>
+      </c>
+      <c r="B269" t="n">
+        <v>13.50045548548957</v>
+      </c>
+      <c r="C269" t="n">
+        <v>1.031793727576375</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>93.79942977967042</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>68</v>
+      </c>
+      <c r="B270" t="n">
+        <v>14.39969529458637</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.8992398090967999</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>81.74907355425452</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>69</v>
+      </c>
+      <c r="B271" t="n">
+        <v>15.42517986984374</v>
+      </c>
+      <c r="C271" t="n">
+        <v>1.025484575257368</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>93.22587047794249</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>70</v>
+      </c>
+      <c r="B272" t="n">
+        <v>16.44471493425692</v>
+      </c>
+      <c r="C272" t="n">
+        <v>1.01953506441318</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>92.68500585574363</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>71</v>
+      </c>
+      <c r="B273" t="n">
+        <v>17.46193100156315</v>
+      </c>
+      <c r="C273" t="n">
+        <v>1.017216067306226</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>92.47418793692961</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>72</v>
+      </c>
+      <c r="B274" t="n">
+        <v>18.47827331141184</v>
+      </c>
+      <c r="C274" t="n">
+        <v>1.016342309848692</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>92.39475544079021</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>73</v>
+      </c>
+      <c r="B275" t="n">
+        <v>19.50547390943064</v>
+      </c>
+      <c r="C275" t="n">
+        <v>1.027200598018805</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>93.38187254716406</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>74</v>
+      </c>
+      <c r="B276" t="n">
+        <v>20.53239868280335</v>
+      </c>
+      <c r="C276" t="n">
+        <v>1.026924773372702</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>93.35679757933654</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>75</v>
+      </c>
+      <c r="B277" t="n">
+        <v>21.54958312657155</v>
+      </c>
+      <c r="C277" t="n">
+        <v>1.017184443768205</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>92.47131306983678</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>76</v>
+      </c>
+      <c r="B278" t="n">
+        <v>22.56353347970808</v>
+      </c>
+      <c r="C278" t="n">
+        <v>1.013950353136533</v>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
+        <v>92.17730483059388</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>77</v>
+      </c>
+      <c r="B279" t="n">
+        <v>23.57694971915037</v>
+      </c>
+      <c r="C279" t="n">
+        <v>1.013416239442282</v>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>92.12874904020748</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>78</v>
+      </c>
+      <c r="B280" t="n">
+        <v>24.59102029567031</v>
+      </c>
+      <c r="C280" t="n">
+        <v>1.014070576519941</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>92.18823422908558</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>79</v>
+      </c>
+      <c r="B281" t="n">
+        <v>25.59992626088454</v>
+      </c>
+      <c r="C281" t="n">
+        <v>1.008905965214229</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>91.71872411038444</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>80</v>
+      </c>
+      <c r="B282" t="n">
+        <v>26.62119735463111</v>
+      </c>
+      <c r="C282" t="n">
+        <v>1.02127109374657</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>92.84282670423364</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>81</v>
+      </c>
+      <c r="B283" t="n">
+        <v>27.64411267913072</v>
+      </c>
+      <c r="C283" t="n">
+        <v>1.022915324499614</v>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>92.99230222723763</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>82</v>
+      </c>
+      <c r="B284" t="n">
+        <v>28.55246431576536</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0.9083516366346345</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>82.5774215122395</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>83</v>
+      </c>
+      <c r="B285" t="n">
+        <v>29.58260757158085</v>
+      </c>
+      <c r="C285" t="n">
+        <v>1.030143255815499</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>93.64938689231811</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>84</v>
+      </c>
+      <c r="B286" t="n">
+        <v>30.60944984094414</v>
+      </c>
+      <c r="C286" t="n">
+        <v>1.026842269363282</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>93.34929721484383</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>85</v>
+      </c>
+      <c r="B287" t="n">
+        <v>31.6370505133951</v>
+      </c>
+      <c r="C287" t="n">
+        <v>1.027600672450959</v>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>93.41824295008713</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>86</v>
+      </c>
+      <c r="B288" t="n">
+        <v>32.66520438797179</v>
+      </c>
+      <c r="C288" t="n">
+        <v>1.028153874576695</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>93.46853405242682</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>87</v>
+      </c>
+      <c r="B289" t="n">
+        <v>33.69425190841343</v>
+      </c>
+      <c r="C289" t="n">
+        <v>1.029047520441644</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>93.54977458560397</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>88</v>
+      </c>
+      <c r="B290" t="n">
+        <v>34.7237284955141</v>
+      </c>
+      <c r="C290" t="n">
+        <v>1.029476587100667</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>93.58878064551521</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>89</v>
+      </c>
+      <c r="B291" t="n">
+        <v>35.75327493838839</v>
+      </c>
+      <c r="C291" t="n">
+        <v>1.029546442874285</v>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F291" t="n">
+        <v>93.59513117038951</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>90</v>
+      </c>
+      <c r="B292" t="n">
+        <v>36.78317877373065</v>
+      </c>
+      <c r="C292" t="n">
+        <v>1.02990383534226</v>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>93.62762139475093</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>91</v>
+      </c>
+      <c r="B293" t="n">
+        <v>37.81345250810672</v>
+      </c>
+      <c r="C293" t="n">
+        <v>1.030273734376074</v>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>93.66124857964307</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>92</v>
+      </c>
+      <c r="B294" t="n">
+        <v>38.84396544689496</v>
+      </c>
+      <c r="C294" t="n">
+        <v>1.030512938788242</v>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>93.68299443529469</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>93</v>
+      </c>
+      <c r="B295" t="n">
+        <v>39.87475685598579</v>
+      </c>
+      <c r="C295" t="n">
+        <v>1.030791409090824</v>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F295" t="n">
+        <v>93.70830991734765</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>94</v>
+      </c>
+      <c r="B296" t="n">
+        <v>40.90564971472482</v>
+      </c>
+      <c r="C296" t="n">
+        <v>1.030892858739037</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>93.71753261263972</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>95</v>
+      </c>
+      <c r="B297" t="n">
+        <v>41.93664161061146</v>
+      </c>
+      <c r="C297" t="n">
+        <v>1.030991895886636</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>93.7265359896942</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>96</v>
+      </c>
+      <c r="B298" t="n">
+        <v>42.96777598485845</v>
+      </c>
+      <c r="C298" t="n">
+        <v>1.031134374246989</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>93.73948856790805</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>97</v>
+      </c>
+      <c r="B299" t="n">
+        <v>43.98767643233218</v>
+      </c>
+      <c r="C299" t="n">
+        <v>1.019900447473731</v>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>92.71822249761188</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>98</v>
+      </c>
+      <c r="B300" t="n">
+        <v>44.99909770400998</v>
+      </c>
+      <c r="C300" t="n">
+        <v>1.011421271677797</v>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F300" t="n">
+        <v>91.94738833434518</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>99</v>
+      </c>
+      <c r="B301" t="n">
+        <v>46.01123702697254</v>
+      </c>
+      <c r="C301" t="n">
+        <v>1.012139322962561</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>92.01266572386918</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>100</v>
+      </c>
+      <c r="B302" t="n">
+        <v>47.02164849916628</v>
+      </c>
+      <c r="C302" t="n">
+        <v>1.010411472193738</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F302" t="n">
+        <v>91.85558838124889</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>101</v>
+      </c>
+      <c r="B303" t="n">
+        <v>48.03031327184228</v>
+      </c>
+      <c r="C303" t="n">
+        <v>1.008664772676006</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F303" t="n">
+        <v>91.69679751600056</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>102</v>
+      </c>
+      <c r="B304" t="n">
+        <v>49.04928466157243</v>
+      </c>
+      <c r="C304" t="n">
+        <v>1.018971389730147</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F304" t="n">
+        <v>92.63376270274067</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>103</v>
+      </c>
+      <c r="B305" t="n">
+        <v>50.07272496334638</v>
+      </c>
+      <c r="C305" t="n">
+        <v>1.023440301773952</v>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F305" t="n">
+        <v>93.04002743399566</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>104</v>
+      </c>
+      <c r="B306" t="n">
+        <v>1.055227807858228</v>
+      </c>
+      <c r="C306" t="n">
+        <v>1.055227807858228</v>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>95.92980071438436</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>105</v>
+      </c>
+      <c r="B307" t="n">
+        <v>2.152336359535838</v>
+      </c>
+      <c r="C307" t="n">
+        <v>1.09710855167761</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F307" t="n">
+        <v>99.73714106160089</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>106</v>
+      </c>
+      <c r="B308" t="n">
+        <v>3.248402406751981</v>
+      </c>
+      <c r="C308" t="n">
+        <v>1.096066047216143</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F308" t="n">
+        <v>99.64236792874026</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>107</v>
+      </c>
+      <c r="B309" t="n">
+        <v>4.34690067396935</v>
+      </c>
+      <c r="C309" t="n">
+        <v>1.098498267217369</v>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F309" t="n">
+        <v>99.86347883794265</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>108</v>
+      </c>
+      <c r="B310" t="n">
+        <v>5.442395319246881</v>
+      </c>
+      <c r="C310" t="n">
+        <v>1.09549464527753</v>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F310" t="n">
+        <v>99.5904222979573</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>109</v>
+      </c>
+      <c r="B311" t="n">
+        <v>6.528327686444055</v>
+      </c>
+      <c r="C311" t="n">
+        <v>1.085932367197175</v>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F311" t="n">
+        <v>98.72112429065223</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>110</v>
+      </c>
+      <c r="B312" t="n">
+        <v>7.610510555314263</v>
+      </c>
+      <c r="C312" t="n">
+        <v>1.082182868870207</v>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F312" t="n">
+        <v>98.38026080638248</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>111</v>
+      </c>
+      <c r="B313" t="n">
+        <v>8.574516439150242</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0.9640058838359797</v>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F313" t="n">
+        <v>87.6368985305436</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>112</v>
+      </c>
+      <c r="B314" t="n">
+        <v>9.654221149713171</v>
+      </c>
+      <c r="C314" t="n">
+        <v>1.079704710562929</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F314" t="n">
+        <v>98.15497368753898</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>113</v>
+      </c>
+      <c r="B315" t="n">
+        <v>10.72449892074099</v>
+      </c>
+      <c r="C315" t="n">
+        <v>1.070277771027818</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F315" t="n">
+        <v>97.29797918434711</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>114</v>
+      </c>
+      <c r="B316" t="n">
+        <v>11.79783540443764</v>
+      </c>
+      <c r="C316" t="n">
+        <v>1.073336483696652</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F316" t="n">
+        <v>97.57604397242289</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>115</v>
+      </c>
+      <c r="B317" t="n">
+        <v>12.86753181894934</v>
+      </c>
+      <c r="C317" t="n">
+        <v>1.069696414511695</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F317" t="n">
+        <v>97.24512859197225</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>116</v>
+      </c>
+      <c r="B318" t="n">
+        <v>13.92931368751159</v>
+      </c>
+      <c r="C318" t="n">
+        <v>1.06178186856225</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F318" t="n">
+        <v>96.52562441474996</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>117</v>
+      </c>
+      <c r="B319" t="n">
+        <v>14.98996193534885</v>
+      </c>
+      <c r="C319" t="n">
+        <v>1.060648247837262</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F319" t="n">
+        <v>96.42256798520566</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>118</v>
+      </c>
+      <c r="B320" t="n">
+        <v>16.04869979098222</v>
+      </c>
+      <c r="C320" t="n">
+        <v>1.058737855633375</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F320" t="n">
+        <v>96.24889596667042</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>119</v>
+      </c>
+      <c r="B321" t="n">
+        <v>17.10470984780661</v>
+      </c>
+      <c r="C321" t="n">
+        <v>1.056010056824391</v>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F321" t="n">
+        <v>96.00091425676281</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>120</v>
+      </c>
+      <c r="B322" t="n">
+        <v>18.15755570797991</v>
+      </c>
+      <c r="C322" t="n">
+        <v>1.052845860173296</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F322" t="n">
+        <v>95.71326001575416</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>121</v>
+      </c>
+      <c r="B323" t="n">
+        <v>19.21329629840527</v>
+      </c>
+      <c r="C323" t="n">
+        <v>1.055740590425362</v>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F323" t="n">
+        <v>95.97641731139655</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>122</v>
+      </c>
+      <c r="B324" t="n">
+        <v>20.26785297271851</v>
+      </c>
+      <c r="C324" t="n">
+        <v>1.054556674313236</v>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F324" t="n">
+        <v>95.86878857393056</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>123</v>
+      </c>
+      <c r="B325" t="n">
+        <v>21.31592457760238</v>
+      </c>
+      <c r="C325" t="n">
+        <v>1.048071604883869</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F325" t="n">
+        <v>95.27923680762449</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>124</v>
+      </c>
+      <c r="B326" t="n">
+        <v>22.36302230864203</v>
+      </c>
+      <c r="C326" t="n">
+        <v>1.047097731039656</v>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F326" t="n">
+        <v>95.19070282178693</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>125</v>
+      </c>
+      <c r="B327" t="n">
+        <v>23.40958807259885</v>
+      </c>
+      <c r="C327" t="n">
+        <v>1.046565763956817</v>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F327" t="n">
+        <v>95.14234217789246</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>126</v>
+      </c>
+      <c r="B328" t="n">
+        <v>24.45450313696585</v>
+      </c>
+      <c r="C328" t="n">
+        <v>1.044915064367004</v>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F328" t="n">
+        <v>94.99227857881851</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>127</v>
+      </c>
+      <c r="B329" t="n">
+        <v>25.49641764462131</v>
+      </c>
+      <c r="C329" t="n">
+        <v>1.041914507655452</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F329" t="n">
+        <v>94.71950069595019</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>128</v>
+      </c>
+      <c r="B330" t="n">
+        <v>26.54341152276324</v>
+      </c>
+      <c r="C330" t="n">
+        <v>1.046993878141937</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F330" t="n">
+        <v>95.18126164926696</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>129</v>
+      </c>
+      <c r="B331" t="n">
+        <v>27.58994365800918</v>
+      </c>
+      <c r="C331" t="n">
+        <v>1.046532135245933</v>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F331" t="n">
+        <v>95.13928502235751</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>130</v>
+      </c>
+      <c r="B332" t="n">
+        <v>28.63551322936792</v>
+      </c>
+      <c r="C332" t="n">
+        <v>1.045569571358747</v>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F332" t="n">
+        <v>95.05177921443158</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>131</v>
+      </c>
+      <c r="B333" t="n">
+        <v>29.67997354684448</v>
+      </c>
+      <c r="C333" t="n">
+        <v>1.044460317476556</v>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F333" t="n">
+        <v>94.95093795241418</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>132</v>
+      </c>
+      <c r="B334" t="n">
+        <v>30.60419036107804</v>
+      </c>
+      <c r="C334" t="n">
+        <v>0.9242168142335565</v>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F334" t="n">
+        <v>84.01971038486876</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>133</v>
+      </c>
+      <c r="B335" t="n">
+        <v>31.652734386474</v>
+      </c>
+      <c r="C335" t="n">
+        <v>1.048544025395962</v>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F335" t="n">
+        <v>95.32218412690567</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>134</v>
+      </c>
+      <c r="B336" t="n">
+        <v>32.6956442238439</v>
+      </c>
+      <c r="C336" t="n">
+        <v>1.042909837369901</v>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F336" t="n">
+        <v>94.80998521544556</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>135</v>
+      </c>
+      <c r="B337" t="n">
+        <v>33.73688905347784</v>
+      </c>
+      <c r="C337" t="n">
+        <v>1.041244829633939</v>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F337" t="n">
+        <v>94.65862087581264</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>136</v>
+      </c>
+      <c r="B338" t="n">
+        <v>34.77700631328825</v>
+      </c>
+      <c r="C338" t="n">
+        <v>1.040117259810415</v>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F338" t="n">
+        <v>94.55611452821957</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>137</v>
+      </c>
+      <c r="B339" t="n">
+        <v>35.8162057436549</v>
+      </c>
+      <c r="C339" t="n">
+        <v>1.039199430366644</v>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F339" t="n">
+        <v>94.47267548787669</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>138</v>
+      </c>
+      <c r="B340" t="n">
+        <v>36.85449819900629</v>
+      </c>
+      <c r="C340" t="n">
+        <v>1.038292455351389</v>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F340" t="n">
+        <v>94.39022321376261</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>139</v>
+      </c>
+      <c r="B341" t="n">
+        <v>37.89181111098656</v>
+      </c>
+      <c r="C341" t="n">
+        <v>1.037312911980273</v>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F341" t="n">
+        <v>94.30117381638841</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>140</v>
+      </c>
+      <c r="B342" t="n">
+        <v>38.92860727213771</v>
+      </c>
+      <c r="C342" t="n">
+        <v>1.036796161151152</v>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F342" t="n">
+        <v>94.25419646828652</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>141</v>
+      </c>
+      <c r="B343" t="n">
+        <v>39.84538864132108</v>
+      </c>
+      <c r="C343" t="n">
+        <v>0.9167813691833686</v>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F343" t="n">
+        <v>83.34376083485169</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>142</v>
+      </c>
+      <c r="B344" t="n">
+        <v>40.88596032476874</v>
+      </c>
+      <c r="C344" t="n">
+        <v>1.040571683447659</v>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F344" t="n">
+        <v>94.59742576796901</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>143</v>
+      </c>
+      <c r="B345" t="n">
+        <v>41.92068077933219</v>
+      </c>
+      <c r="C345" t="n">
+        <v>1.034720454563455</v>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F345" t="n">
+        <v>94.06549586940503</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>144</v>
+      </c>
+      <c r="B346" t="n">
+        <v>42.83435146222249</v>
+      </c>
+      <c r="C346" t="n">
+        <v>0.9136706828902987</v>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F346" t="n">
+        <v>83.06097117184534</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>145</v>
+      </c>
+      <c r="B347" t="n">
+        <v>43.86653826237493</v>
+      </c>
+      <c r="C347" t="n">
+        <v>1.032186800152438</v>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F347" t="n">
+        <v>93.83516365022162</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>146</v>
+      </c>
+      <c r="B348" t="n">
+        <v>44.88713482412205</v>
+      </c>
+      <c r="C348" t="n">
+        <v>1.020596561747119</v>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F348" t="n">
+        <v>92.78150561337448</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>147</v>
+      </c>
+      <c r="B349" t="n">
+        <v>45.90639034647801</v>
+      </c>
+      <c r="C349" t="n">
+        <v>1.019255522355955</v>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F349" t="n">
+        <v>92.65959294145047</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>148</v>
+      </c>
+      <c r="B350" t="n">
+        <v>46.92391518635001</v>
+      </c>
+      <c r="C350" t="n">
+        <v>1.017524839872003</v>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F350" t="n">
+        <v>92.50225817018207</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>1</v>
+      </c>
+      <c r="B351" t="n">
+        <v>1.16241194625815</v>
+      </c>
+      <c r="C351" t="n">
+        <v>1.16241194625815</v>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F351" t="n">
+        <v>105.6738132961954</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>2</v>
+      </c>
+      <c r="B352" t="n">
+        <v>1.140773820517232</v>
+      </c>
+      <c r="C352" t="n">
+        <v>1.140773820517232</v>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F352" t="n">
+        <v>103.706710956112</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>3</v>
+      </c>
+      <c r="B353" t="n">
+        <v>1.139105930615482</v>
+      </c>
+      <c r="C353" t="n">
+        <v>1.139105930615482</v>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F353" t="n">
+        <v>103.5550846014075</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>4</v>
+      </c>
+      <c r="B354" t="n">
+        <v>1.138543595376723</v>
+      </c>
+      <c r="C354" t="n">
+        <v>1.138543595376723</v>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F354" t="n">
+        <v>103.5039632160657</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>5</v>
+      </c>
+      <c r="B355" t="n">
+        <v>2.276498796615165</v>
+      </c>
+      <c r="C355" t="n">
+        <v>1.137955201238442</v>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F355" t="n">
+        <v>103.4504728398584</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>6</v>
+      </c>
+      <c r="B356" t="n">
+        <v>3.413179106350995</v>
+      </c>
+      <c r="C356" t="n">
+        <v>1.13668030973583</v>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F356" t="n">
+        <v>103.3345736123482</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>7</v>
+      </c>
+      <c r="B357" t="n">
+        <v>4.547398499644769</v>
+      </c>
+      <c r="C357" t="n">
+        <v>1.134219393293774</v>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F357" t="n">
+        <v>103.1108539357977</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>8</v>
+      </c>
+      <c r="B358" t="n">
+        <v>5.671115152841734</v>
+      </c>
+      <c r="C358" t="n">
+        <v>1.123716653196965</v>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F358" t="n">
+        <v>102.1560593815423</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>9</v>
+      </c>
+      <c r="B359" t="n">
+        <v>6.785802736033912</v>
+      </c>
+      <c r="C359" t="n">
+        <v>1.114687583192178</v>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F359" t="n">
+        <v>101.3352348356525</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>10</v>
+      </c>
+      <c r="B360" t="n">
+        <v>7.896140661276919</v>
+      </c>
+      <c r="C360" t="n">
+        <v>1.110337925243007</v>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F360" t="n">
+        <v>100.9398113857279</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>11</v>
+      </c>
+      <c r="B361" t="n">
+        <v>9.003128063043921</v>
+      </c>
+      <c r="C361" t="n">
+        <v>1.106987401767001</v>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F361" t="n">
+        <v>100.6352183424546</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>12</v>
+      </c>
+      <c r="B362" t="n">
+        <v>10.10719936217718</v>
+      </c>
+      <c r="C362" t="n">
+        <v>1.104071299133263</v>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F362" t="n">
+        <v>100.3701181030239</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>13</v>
+      </c>
+      <c r="B363" t="n">
+        <v>11.21830930616636</v>
+      </c>
+      <c r="C363" t="n">
+        <v>1.111109943989181</v>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F363" t="n">
+        <v>101.0099949081074</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>14</v>
+      </c>
+      <c r="B364" t="n">
+        <v>12.33129184444021</v>
+      </c>
+      <c r="C364" t="n">
+        <v>1.112982538273844</v>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F364" t="n">
+        <v>101.1802307521676</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>15</v>
+      </c>
+      <c r="B365" t="n">
+        <v>13.44429821496854</v>
+      </c>
+      <c r="C365" t="n">
+        <v>1.113006370528336</v>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F365" t="n">
+        <v>101.1823973207578</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>16</v>
+      </c>
+      <c r="B366" t="n">
+        <v>14.55696321107396</v>
+      </c>
+      <c r="C366" t="n">
+        <v>1.112664996105419</v>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F366" t="n">
+        <v>101.1513632823108</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>17</v>
+      </c>
+      <c r="B367" t="n">
+        <v>15.66905977805289</v>
+      </c>
+      <c r="C367" t="n">
+        <v>1.112096566978929</v>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F367" t="n">
+        <v>101.0996879071753</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>18</v>
+      </c>
+      <c r="B368" t="n">
+        <v>16.78078183103145</v>
+      </c>
+      <c r="C368" t="n">
+        <v>1.111722052978559</v>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F368" t="n">
+        <v>101.065641179869</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>19</v>
+      </c>
+      <c r="B369" t="n">
+        <v>17.8917186480297</v>
+      </c>
+      <c r="C369" t="n">
+        <v>1.110936816998251</v>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F369" t="n">
+        <v>100.9942560907501</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>20</v>
+      </c>
+      <c r="B370" t="n">
+        <v>19.00215402491973</v>
+      </c>
+      <c r="C370" t="n">
+        <v>1.110435376890031</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F370" t="n">
+        <v>100.9486706263665</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>21</v>
+      </c>
+      <c r="B371" t="n">
+        <v>20.11174053883676</v>
+      </c>
+      <c r="C371" t="n">
+        <v>1.10958651391703</v>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F371" t="n">
+        <v>100.8715012651845</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>22</v>
+      </c>
+      <c r="B372" t="n">
+        <v>21.22055567953404</v>
+      </c>
+      <c r="C372" t="n">
+        <v>1.108815140697281</v>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F372" t="n">
+        <v>100.8013764270256</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>23</v>
+      </c>
+      <c r="B373" t="n">
+        <v>22.32876013317005</v>
+      </c>
+      <c r="C373" t="n">
+        <v>1.108204453636006</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F373" t="n">
+        <v>100.7458594214551</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>24</v>
+      </c>
+      <c r="B374" t="n">
+        <v>23.43637941065311</v>
+      </c>
+      <c r="C374" t="n">
+        <v>1.10761927748306</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F374" t="n">
+        <v>100.6926615893691</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>25</v>
+      </c>
+      <c r="B375" t="n">
+        <v>24.54330866647413</v>
+      </c>
+      <c r="C375" t="n">
+        <v>1.106929255821022</v>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F375" t="n">
+        <v>100.6299323473656</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>26</v>
+      </c>
+      <c r="B376" t="n">
+        <v>25.64969708119986</v>
+      </c>
+      <c r="C376" t="n">
+        <v>1.106388414725725</v>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F376" t="n">
+        <v>100.5807649750659</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>27</v>
+      </c>
+      <c r="B377" t="n">
+        <v>26.75530855498607</v>
+      </c>
+      <c r="C377" t="n">
+        <v>1.105611473786208</v>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F377" t="n">
+        <v>100.5101339805644</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>28</v>
+      </c>
+      <c r="B378" t="n">
+        <v>27.8584226802503</v>
+      </c>
+      <c r="C378" t="n">
+        <v>1.103114125264234</v>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F378" t="n">
+        <v>100.2831022967486</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>29</v>
+      </c>
+      <c r="B379" t="n">
+        <v>28.94836323080262</v>
+      </c>
+      <c r="C379" t="n">
+        <v>1.089940550552317</v>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F379" t="n">
+        <v>99.08550459566517</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>30</v>
+      </c>
+      <c r="B380" t="n">
+        <v>30.03335032605572</v>
+      </c>
+      <c r="C380" t="n">
+        <v>1.084987095253105</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F380" t="n">
+        <v>98.63519047755499</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>31</v>
+      </c>
+      <c r="B381" t="n">
+        <v>31.11533872147519</v>
+      </c>
+      <c r="C381" t="n">
+        <v>1.081988395419472</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F381" t="n">
+        <v>98.3625814017702</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>32</v>
+      </c>
+      <c r="B382" t="n">
+        <v>32.19464481784028</v>
+      </c>
+      <c r="C382" t="n">
+        <v>1.079306096365091</v>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F382" t="n">
+        <v>98.11873603319007</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>33</v>
+      </c>
+      <c r="B383" t="n">
+        <v>33.27351385051168</v>
+      </c>
+      <c r="C383" t="n">
+        <v>1.078869032671392</v>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F383" t="n">
+        <v>98.07900297012652</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>34</v>
+      </c>
+      <c r="B384" t="n">
+        <v>34.36338568439516</v>
+      </c>
+      <c r="C384" t="n">
+        <v>1.089871833883485</v>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F384" t="n">
+        <v>99.07925762577139</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>35</v>
+      </c>
+      <c r="B385" t="n">
+        <v>35.45332968915602</v>
+      </c>
+      <c r="C385" t="n">
+        <v>1.089944004760859</v>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F385" t="n">
+        <v>99.08581861462356</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>36</v>
+      </c>
+      <c r="B386" t="n">
+        <v>36.53058146010321</v>
+      </c>
+      <c r="C386" t="n">
+        <v>1.077251770947186</v>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F386" t="n">
+        <v>97.93197917701687</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>37</v>
+      </c>
+      <c r="B387" t="n">
+        <v>37.60209236610033</v>
+      </c>
+      <c r="C387" t="n">
+        <v>1.071510905997123</v>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F387" t="n">
+        <v>97.41008236337477</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>38</v>
+      </c>
+      <c r="B388" t="n">
+        <v>38.67384202696605</v>
+      </c>
+      <c r="C388" t="n">
+        <v>1.07174966086572</v>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F388" t="n">
+        <v>97.43178735142908</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>39</v>
+      </c>
+      <c r="B389" t="n">
+        <v>39.74377372914694</v>
+      </c>
+      <c r="C389" t="n">
+        <v>1.069931702180888</v>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F389" t="n">
+        <v>97.26651838008073</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>40</v>
+      </c>
+      <c r="B390" t="n">
+        <v>40.81482844298118</v>
+      </c>
+      <c r="C390" t="n">
+        <v>1.071054713834243</v>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F390" t="n">
+        <v>97.36861034856757</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>41</v>
+      </c>
+      <c r="B391" t="n">
+        <v>41.89605911253297</v>
+      </c>
+      <c r="C391" t="n">
+        <v>1.081230669551793</v>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F391" t="n">
+        <v>98.2936972319812</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>42</v>
+      </c>
+      <c r="B392" t="n">
+        <v>42.97723465631597</v>
+      </c>
+      <c r="C392" t="n">
+        <v>1.081175543782997</v>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F392" t="n">
+        <v>98.2886857984543</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>43</v>
+      </c>
+      <c r="B393" t="n">
+        <v>44.04587416026572</v>
+      </c>
+      <c r="C393" t="n">
+        <v>1.068639503949747</v>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F393" t="n">
+        <v>97.14904581361336</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>44</v>
+      </c>
+      <c r="B394" t="n">
+        <v>45.11145101693138</v>
+      </c>
+      <c r="C394" t="n">
+        <v>1.065576856665658</v>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F394" t="n">
+        <v>96.8706233332416</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>45</v>
+      </c>
+      <c r="B395" t="n">
+        <v>46.17707228063038</v>
+      </c>
+      <c r="C395" t="n">
+        <v>1.065621263699001</v>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F395" t="n">
+        <v>96.87466033627277</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>46</v>
+      </c>
+      <c r="B396" t="n">
+        <v>47.24233115472096</v>
+      </c>
+      <c r="C396" t="n">
+        <v>1.065258874090581</v>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F396" t="n">
+        <v>96.84171582641648</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>47</v>
+      </c>
+      <c r="B397" t="n">
+        <v>48.30578414269559</v>
+      </c>
+      <c r="C397" t="n">
+        <v>1.063452987974628</v>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F397" t="n">
+        <v>96.67754436132982</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>48</v>
+      </c>
+      <c r="B398" t="n">
+        <v>49.37966443932519</v>
+      </c>
+      <c r="C398" t="n">
+        <v>1.073880296629603</v>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F398" t="n">
+        <v>97.62548151178213</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>49</v>
+      </c>
+      <c r="B399" t="n">
+        <v>50.45417232904504</v>
+      </c>
+      <c r="C399" t="n">
+        <v>1.074507889719854</v>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F399" t="n">
+        <v>97.68253542907762</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>50</v>
+      </c>
+      <c r="B400" t="n">
+        <v>51.51861887799857</v>
+      </c>
+      <c r="C400" t="n">
+        <v>1.064446548953526</v>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F400" t="n">
+        <v>96.76786808668422</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>51</v>
+      </c>
+      <c r="B401" t="n">
+        <v>52.57995435510261</v>
+      </c>
+      <c r="C401" t="n">
+        <v>1.061335477104045</v>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F401" t="n">
+        <v>96.48504337309498</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>52</v>
+      </c>
+      <c r="B402" t="n">
+        <v>53.6398951031152</v>
+      </c>
+      <c r="C402" t="n">
+        <v>1.059940748012586</v>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F402" t="n">
+        <v>96.35824981932602</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>53</v>
+      </c>
+      <c r="B403" t="n">
         <v>54.69869301159702</v>
       </c>
-      <c r="C163" t="n">
+      <c r="C403" t="n">
         <v>1.058797908481822</v>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D403" t="inlineStr">
         <is>
           <t>CS2_38</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F163" t="n">
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F403" t="n">
         <v>96.25435531652923</v>
       </c>
     </row>

--- a/reports/Master_Retention_Summary.xlsx
+++ b/reports/Master_Retention_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F403"/>
+  <dimension ref="A1:F446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10108,6 +10108,1038 @@
         <v>96.25435531652923</v>
       </c>
     </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>54</v>
+      </c>
+      <c r="B404" t="n">
+        <v>1.061577545637317</v>
+      </c>
+      <c r="C404" t="n">
+        <v>1.061577545637317</v>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F404" t="n">
+        <v>96.50704960339246</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>55</v>
+      </c>
+      <c r="B405" t="n">
+        <v>2.164289885491261</v>
+      </c>
+      <c r="C405" t="n">
+        <v>1.102712339853944</v>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F405" t="n">
+        <v>100.2465763503585</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>56</v>
+      </c>
+      <c r="B406" t="n">
+        <v>3.267583323939062</v>
+      </c>
+      <c r="C406" t="n">
+        <v>1.103293438447801</v>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F406" t="n">
+        <v>100.2994034952546</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>57</v>
+      </c>
+      <c r="B407" t="n">
+        <v>4.372056985656962</v>
+      </c>
+      <c r="C407" t="n">
+        <v>1.1044736617179</v>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F407" t="n">
+        <v>100.4066965198091</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>58</v>
+      </c>
+      <c r="B408" t="n">
+        <v>5.473847553432576</v>
+      </c>
+      <c r="C408" t="n">
+        <v>1.101790567775614</v>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F408" t="n">
+        <v>100.1627788886922</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>59</v>
+      </c>
+      <c r="B409" t="n">
+        <v>6.565619223003772</v>
+      </c>
+      <c r="C409" t="n">
+        <v>1.091771669571195</v>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F409" t="n">
+        <v>99.25196996101776</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>60</v>
+      </c>
+      <c r="B410" t="n">
+        <v>7.653588180894634</v>
+      </c>
+      <c r="C410" t="n">
+        <v>1.087968957890863</v>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F410" t="n">
+        <v>98.90626889916932</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>61</v>
+      </c>
+      <c r="B411" t="n">
+        <v>8.739329367509095</v>
+      </c>
+      <c r="C411" t="n">
+        <v>1.08574118661446</v>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F411" t="n">
+        <v>98.70374423767821</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>62</v>
+      </c>
+      <c r="B412" t="n">
+        <v>9.819657743935954</v>
+      </c>
+      <c r="C412" t="n">
+        <v>1.080328376426859</v>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F412" t="n">
+        <v>98.21167058425992</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>63</v>
+      </c>
+      <c r="B413" t="n">
+        <v>10.90013606510165</v>
+      </c>
+      <c r="C413" t="n">
+        <v>1.080478321165694</v>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F413" t="n">
+        <v>98.22530192415402</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>64</v>
+      </c>
+      <c r="B414" t="n">
+        <v>11.9795786581839</v>
+      </c>
+      <c r="C414" t="n">
+        <v>1.079442593082256</v>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F414" t="n">
+        <v>98.13114482565959</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>65</v>
+      </c>
+      <c r="B415" t="n">
+        <v>13.05247552649116</v>
+      </c>
+      <c r="C415" t="n">
+        <v>1.072896868307252</v>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F415" t="n">
+        <v>97.53607893702289</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>66</v>
+      </c>
+      <c r="B416" t="n">
+        <v>14.12108721883883</v>
+      </c>
+      <c r="C416" t="n">
+        <v>1.068611692347671</v>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F416" t="n">
+        <v>97.14651748615194</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>67</v>
+      </c>
+      <c r="B417" t="n">
+        <v>15.18801044751135</v>
+      </c>
+      <c r="C417" t="n">
+        <v>1.066923228672525</v>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F417" t="n">
+        <v>96.9930207884114</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>68</v>
+      </c>
+      <c r="B418" t="n">
+        <v>16.25279605790751</v>
+      </c>
+      <c r="C418" t="n">
+        <v>1.064785610396154</v>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F418" t="n">
+        <v>96.79869185419578</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>69</v>
+      </c>
+      <c r="B419" t="n">
+        <v>17.14256780443614</v>
+      </c>
+      <c r="C419" t="n">
+        <v>0.8897717465286341</v>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F419" t="n">
+        <v>80.88834059351218</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>70</v>
+      </c>
+      <c r="B420" t="n">
+        <v>18.20948826116475</v>
+      </c>
+      <c r="C420" t="n">
+        <v>1.066920456728607</v>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F420" t="n">
+        <v>96.99276879350968</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>71</v>
+      </c>
+      <c r="B421" t="n">
+        <v>19.2714905333444</v>
+      </c>
+      <c r="C421" t="n">
+        <v>1.062002272179654</v>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F421" t="n">
+        <v>96.54566110724132</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>72</v>
+      </c>
+      <c r="B422" t="n">
+        <v>20.33037048751444</v>
+      </c>
+      <c r="C422" t="n">
+        <v>1.058879954170042</v>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F422" t="n">
+        <v>96.26181401545834</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>73</v>
+      </c>
+      <c r="B423" t="n">
+        <v>21.38314339519933</v>
+      </c>
+      <c r="C423" t="n">
+        <v>1.052772907684886</v>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F423" t="n">
+        <v>95.7066279713533</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>74</v>
+      </c>
+      <c r="B424" t="n">
+        <v>22.43621759374313</v>
+      </c>
+      <c r="C424" t="n">
+        <v>1.053074198543797</v>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F424" t="n">
+        <v>95.73401804943609</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>75</v>
+      </c>
+      <c r="B425" t="n">
+        <v>23.48822786663382</v>
+      </c>
+      <c r="C425" t="n">
+        <v>1.052010272890691</v>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F425" t="n">
+        <v>95.63729753551732</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>76</v>
+      </c>
+      <c r="B426" t="n">
+        <v>24.53769265857875</v>
+      </c>
+      <c r="C426" t="n">
+        <v>1.049464791944928</v>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F426" t="n">
+        <v>95.40589017681161</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>77</v>
+      </c>
+      <c r="B427" t="n">
+        <v>25.59265457381279</v>
+      </c>
+      <c r="C427" t="n">
+        <v>1.054961915234045</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F427" t="n">
+        <v>95.90562865764049</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>78</v>
+      </c>
+      <c r="B428" t="n">
+        <v>26.64747142294459</v>
+      </c>
+      <c r="C428" t="n">
+        <v>1.0548168491318</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F428" t="n">
+        <v>95.89244083016365</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>79</v>
+      </c>
+      <c r="B429" t="n">
+        <v>27.70105142219042</v>
+      </c>
+      <c r="C429" t="n">
+        <v>1.053579999245834</v>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F429" t="n">
+        <v>95.77999993143942</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>80</v>
+      </c>
+      <c r="B430" t="n">
+        <v>28.75368506607596</v>
+      </c>
+      <c r="C430" t="n">
+        <v>1.052633643885539</v>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F430" t="n">
+        <v>95.69396762595807</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>81</v>
+      </c>
+      <c r="B431" t="n">
+        <v>29.80563104953838</v>
+      </c>
+      <c r="C431" t="n">
+        <v>1.051945983462417</v>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F431" t="n">
+        <v>95.63145304203792</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>82</v>
+      </c>
+      <c r="B432" t="n">
+        <v>30.8575977483636</v>
+      </c>
+      <c r="C432" t="n">
+        <v>1.051966698825215</v>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F432" t="n">
+        <v>95.63333625683769</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>83</v>
+      </c>
+      <c r="B433" t="n">
+        <v>31.90853479851857</v>
+      </c>
+      <c r="C433" t="n">
+        <v>1.050937050154975</v>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F433" t="n">
+        <v>95.53973183227042</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>84</v>
+      </c>
+      <c r="B434" t="n">
+        <v>32.95801188122525</v>
+      </c>
+      <c r="C434" t="n">
+        <v>1.049477082706677</v>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F434" t="n">
+        <v>95.40700751878877</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>85</v>
+      </c>
+      <c r="B435" t="n">
+        <v>34.00615073531269</v>
+      </c>
+      <c r="C435" t="n">
+        <v>1.048138854087448</v>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F435" t="n">
+        <v>95.28535037158615</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>86</v>
+      </c>
+      <c r="B436" t="n">
+        <v>35.05383725842688</v>
+      </c>
+      <c r="C436" t="n">
+        <v>1.047686523114187</v>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F436" t="n">
+        <v>95.24422937401701</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>87</v>
+      </c>
+      <c r="B437" t="n">
+        <v>36.10048850578645</v>
+      </c>
+      <c r="C437" t="n">
+        <v>1.04665124735957</v>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F437" t="n">
+        <v>95.15011339632453</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>88</v>
+      </c>
+      <c r="B438" t="n">
+        <v>36.98470135955655</v>
+      </c>
+      <c r="C438" t="n">
+        <v>0.8842128537701015</v>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F438" t="n">
+        <v>80.38298670637286</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>89</v>
+      </c>
+      <c r="B439" t="n">
+        <v>38.03563074689517</v>
+      </c>
+      <c r="C439" t="n">
+        <v>1.050929387338613</v>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F439" t="n">
+        <v>95.53903521260115</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>90</v>
+      </c>
+      <c r="B440" t="n">
+        <v>39.08096058531849</v>
+      </c>
+      <c r="C440" t="n">
+        <v>1.045329838423321</v>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F440" t="n">
+        <v>95.02998531121096</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>91</v>
+      </c>
+      <c r="B441" t="n">
+        <v>40.124614391113</v>
+      </c>
+      <c r="C441" t="n">
+        <v>1.043653805794513</v>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F441" t="n">
+        <v>94.87761870859207</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>92</v>
+      </c>
+      <c r="B442" t="n">
+        <v>41.16745894009971</v>
+      </c>
+      <c r="C442" t="n">
+        <v>1.042844548986714</v>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F442" t="n">
+        <v>94.80404990788313</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>93</v>
+      </c>
+      <c r="B443" t="n">
+        <v>42.20830582705204</v>
+      </c>
+      <c r="C443" t="n">
+        <v>1.040846886952323</v>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F443" t="n">
+        <v>94.62244426839302</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>94</v>
+      </c>
+      <c r="B444" t="n">
+        <v>43.23699830529267</v>
+      </c>
+      <c r="C444" t="n">
+        <v>1.028692478240629</v>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F444" t="n">
+        <v>93.51749802187534</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>95</v>
+      </c>
+      <c r="B445" t="n">
+        <v>44.26474272593617</v>
+      </c>
+      <c r="C445" t="n">
+        <v>1.027744420643508</v>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F445" t="n">
+        <v>93.43131096759161</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>96</v>
+      </c>
+      <c r="B446" t="n">
+        <v>45.29112759404217</v>
+      </c>
+      <c r="C446" t="n">
+        <v>1.026384868105993</v>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F446" t="n">
+        <v>93.30771528236296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/Master_Retention_Summary.xlsx
+++ b/reports/Master_Retention_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,17 +486,17 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1.160620725192767</v>
+        <v>1.138645812632654</v>
       </c>
       <c r="C3" t="n">
-        <v>1.160620725192767</v>
+        <v>1.138645812632654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>105.5109750175243</v>
+        <v>103.5132556938776</v>
       </c>
     </row>
     <row r="4">
@@ -513,14 +513,14 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>1.153332504667897</v>
+        <v>1.160620725192767</v>
       </c>
       <c r="C4" t="n">
-        <v>1.153332504667897</v>
+        <v>1.160620725192767</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CS2_37</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>104.8484095152634</v>
+        <v>105.5109750175243</v>
       </c>
     </row>
     <row r="5">
@@ -537,22 +537,46 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
+        <v>1.153332504667897</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.153332504667897</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>104.8484095152634</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
         <v>1.16241194625815</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C6" t="n">
         <v>1.16241194625815</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>CS2_38</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Ambient</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F6" t="n">
         <v>105.6738132961954</v>
       </c>
     </row>

--- a/reports/Master_Retention_Summary.xlsx
+++ b/reports/Master_Retention_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,17 +534,17 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="n">
-        <v>1.153332504667897</v>
+        <v>1.145706012058183</v>
       </c>
       <c r="C5" t="n">
-        <v>1.153332504667897</v>
+        <v>1.145706012058183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CS2_37</t>
+          <t>CS2_36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>104.8484095152634</v>
+        <v>104.1550920052894</v>
       </c>
     </row>
     <row r="6">
@@ -561,22 +561,46 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
+        <v>1.153332504667897</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.153332504667897</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>104.8484095152634</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
         <v>1.16241194625815</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>1.16241194625815</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>CS2_38</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Ambient</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
         <v>105.6738132961954</v>
       </c>
     </row>

--- a/reports/Master_Retention_Summary.xlsx
+++ b/reports/Master_Retention_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,25 +582,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1.134444845802931</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.134444845802931</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>103.1313496184483</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>1</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B8" t="n">
         <v>1.16241194625815</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C8" t="n">
         <v>1.16241194625815</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>CS2_38</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Ambient</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F8" t="n">
         <v>105.6738132961954</v>
       </c>
     </row>

--- a/reports/Master_Retention_Summary.xlsx
+++ b/reports/Master_Retention_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,6 +628,30 @@
         <v>105.6738132961954</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1.140773820517232</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.140773820517232</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>103.706710956112</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/Master_Retention_Summary.xlsx
+++ b/reports/Master_Retention_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,6 +652,30 @@
         <v>103.706710956112</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1.139105930615482</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.139105930615482</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>103.5550846014075</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/Master_Retention_Summary.xlsx
+++ b/reports/Master_Retention_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,17 +510,17 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1.160620725192767</v>
+        <v>1.052322023911945</v>
       </c>
       <c r="C4" t="n">
-        <v>1.160620725192767</v>
+        <v>1.052322023911945</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -529,22 +529,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>105.5109750175243</v>
+        <v>95.66563853744955</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1.145706012058183</v>
+        <v>2.149665492833128</v>
       </c>
       <c r="C5" t="n">
-        <v>1.145706012058183</v>
+        <v>1.097343468921183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -553,22 +553,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>104.1550920052894</v>
+        <v>99.75849717465297</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1.153332504667897</v>
+        <v>3.245035743823332</v>
       </c>
       <c r="C6" t="n">
-        <v>1.153332504667897</v>
+        <v>1.095370250990204</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CS2_37</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -577,22 +577,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>104.8484095152634</v>
+        <v>99.57911372638219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1.134444845802931</v>
+        <v>4.3427396829912</v>
       </c>
       <c r="C7" t="n">
-        <v>1.134444845802931</v>
+        <v>1.097703939167868</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CS2_37</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -601,22 +601,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>103.1313496184483</v>
+        <v>99.79126719707895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1.16241194625815</v>
+        <v>5.438155466960088</v>
       </c>
       <c r="C8" t="n">
-        <v>1.16241194625815</v>
+        <v>1.095415783968887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -625,22 +625,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>105.6738132961954</v>
+        <v>99.58325308808065</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1.140773820517232</v>
+        <v>6.408604373024617</v>
       </c>
       <c r="C9" t="n">
-        <v>1.140773820517232</v>
+        <v>0.9704489060645294</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -649,30 +649,1110 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>103.706710956112</v>
+        <v>88.22262782404812</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>7.495652225355175</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.087047852330558</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>98.82253203005074</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8.577396784697651</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.081744559342476</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>98.34041448567962</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>9.654946259914045</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.077549475216394</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>97.95904320149033</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>10.72613836450355</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.071192104589505</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>97.38110041722771</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>11.79860684954863</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.072468485045077</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>97.49713500409788</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>12.86786434001764</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.069257490469012</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>97.20522640627377</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>13.9297296638013</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.061865323783662</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>96.53321125306019</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>14.98952004353151</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.05979037973021</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>96.34457997547359</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>16.04749855873573</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.057978515204223</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>96.17986501856569</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17.10340536937683</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.055906810641098</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>95.99152824009978</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>18.1556290521891</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.052223682812269</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>95.65669843747897</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>19.20997154058639</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.054342488397296</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>95.84931712702691</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>20.26299732771692</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.053025787130522</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>95.72961701186567</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>21.31033341195971</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.047336084242794</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>95.21237129479941</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>22.35610598333428</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.045772571374567</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>95.07023376132425</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>23.40056677922347</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.044460795889197</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>94.95098144447246</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>24.44359582009594</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.043029040872465</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>94.82082189749683</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>25.4831948218273</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.039599001731357</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>94.5090001573961</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>26.52631445530069</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.043119633473388</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>94.82905758848985</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>27.5686670992941</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.042352643993418</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>94.75933127212889</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>28.60979222529076</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.041125125996658</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>94.64773872696887</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>29.64938541586051</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.03959319056975</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>94.50847186997728</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>30.68792447367722</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.038539057816706</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>94.41264161970055</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>31.7263162152612</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.038391741583983</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>94.39924923490749</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>32.76338812831584</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.037071913054639</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>94.27926482314901</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>33.7987298481729</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.035341719857065</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>94.12197453246048</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>34.83270037940027</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1.033970531227368</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>93.9973210206698</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>35.86574666724295</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1.033046287842673</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>93.91329889478844</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>36.89740618197521</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1.031659514732269</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>93.78722861202442</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>37.92829661484846</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.030890432873242</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>93.71731207938568</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>38.95850830029624</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.030211685447789</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>93.65560776798078</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>39.98860228884588</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.030093988549631</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>93.6449080499664</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="n">
+        <v>41.01705848167371</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.028456192827839</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>93.49601752980357</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="n">
+        <v>42.04438475344786</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.027326271774143</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>93.39329743401301</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="n">
+        <v>43.07010828743945</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1.025723533991588</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>93.24759399923526</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="n">
+        <v>44.08658300417674</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1.016474716737292</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>92.40679243066293</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>45.10024541836556</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1.013662414188822</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>92.15112856262017</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>46.1126554106551</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1.012409992289541</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>92.03727202632192</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="n">
+        <v>46.39238602108801</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.2797306104329067</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>25.4300554939006</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1.160620725192767</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1.160620725192767</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>105.5109750175243</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1.145706012058183</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.145706012058183</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>104.1550920052894</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1.153332504667897</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1.153332504667897</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>104.8484095152634</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1.134444845802931</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1.134444845802931</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>103.1313496184483</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1.16241194625815</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1.16241194625815</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>105.6738132961954</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1.140773820517232</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1.140773820517232</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>103.706710956112</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
         <v>3</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B55" t="n">
         <v>1.139105930615482</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C55" t="n">
         <v>1.139105930615482</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>CS2_38</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
         <v>103.5550846014075</v>
       </c>
     </row>

--- a/reports/Master_Retention_Summary.xlsx
+++ b/reports/Master_Retention_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,10 +513,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1.052322023911945</v>
+        <v>1.137456760812122</v>
       </c>
       <c r="C4" t="n">
-        <v>1.052322023911945</v>
+        <v>1.137456760812122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>95.66563853744955</v>
+        <v>103.4051600738293</v>
       </c>
     </row>
     <row r="5">
@@ -537,10 +537,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2.149665492833128</v>
+        <v>1.137011583397129</v>
       </c>
       <c r="C5" t="n">
-        <v>1.097343468921183</v>
+        <v>1.137011583397129</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>99.75849717465297</v>
+        <v>103.364689399739</v>
       </c>
     </row>
     <row r="6">
@@ -561,10 +561,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3.245035743823332</v>
+        <v>2.273810507318694</v>
       </c>
       <c r="C6" t="n">
-        <v>1.095370250990204</v>
+        <v>1.136798923921565</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>99.57911372638219</v>
+        <v>103.3453567201422</v>
       </c>
     </row>
     <row r="7">
@@ -585,10 +585,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>4.3427396829912</v>
+        <v>3.406011953491648</v>
       </c>
       <c r="C7" t="n">
-        <v>1.097703939167868</v>
+        <v>1.132201446172954</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>99.79126719707895</v>
+        <v>102.9274041975413</v>
       </c>
     </row>
     <row r="8">
@@ -609,10 +609,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>5.438155466960088</v>
+        <v>4.535073167063902</v>
       </c>
       <c r="C8" t="n">
-        <v>1.095415783968887</v>
+        <v>1.129061213572254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>99.58325308808065</v>
+        <v>102.6419285065685</v>
       </c>
     </row>
     <row r="9">
@@ -633,10 +633,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>6.408604373024617</v>
+        <v>5.65538205316819</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9704489060645294</v>
+        <v>1.120308886104288</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>88.22262782404812</v>
+        <v>101.8462623731171</v>
       </c>
     </row>
     <row r="10">
@@ -657,10 +657,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>7.495652225355175</v>
+        <v>6.765709906183314</v>
       </c>
       <c r="C10" t="n">
-        <v>1.087047852330558</v>
+        <v>1.110327853015124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>98.82253203005074</v>
+        <v>100.9388957286477</v>
       </c>
     </row>
     <row r="11">
@@ -681,10 +681,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>8.577396784697651</v>
+        <v>7.871236454520941</v>
       </c>
       <c r="C11" t="n">
-        <v>1.081744559342476</v>
+        <v>1.105526548337626</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>98.34041448567962</v>
+        <v>100.5024134852387</v>
       </c>
     </row>
     <row r="12">
@@ -705,10 +705,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>9.654946259914045</v>
+        <v>8.973180416597838</v>
       </c>
       <c r="C12" t="n">
-        <v>1.077549475216394</v>
+        <v>1.101943962076898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>97.95904320149033</v>
+        <v>100.1767238251725</v>
       </c>
     </row>
     <row r="13">
@@ -729,10 +729,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>10.72613836450355</v>
+        <v>10.07175905337804</v>
       </c>
       <c r="C13" t="n">
-        <v>1.071192104589505</v>
+        <v>1.098578636780204</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>97.38110041722771</v>
+        <v>99.87078516183668</v>
       </c>
     </row>
     <row r="14">
@@ -753,10 +753,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>11.79860684954863</v>
+        <v>11.17652816931319</v>
       </c>
       <c r="C14" t="n">
-        <v>1.072468485045077</v>
+        <v>1.104769115935152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>97.49713500409788</v>
+        <v>100.4335559941048</v>
       </c>
     </row>
     <row r="15">
@@ -777,10 +777,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>12.86786434001764</v>
+        <v>12.28214775502528</v>
       </c>
       <c r="C15" t="n">
-        <v>1.069257490469012</v>
+        <v>1.105619585712086</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>97.20522640627377</v>
+        <v>100.5108714283714</v>
       </c>
     </row>
     <row r="16">
@@ -801,10 +801,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>13.9297296638013</v>
+        <v>13.38758978184518</v>
       </c>
       <c r="C16" t="n">
-        <v>1.061865323783662</v>
+        <v>1.105442026819896</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>96.53321125306019</v>
+        <v>100.4947297108996</v>
       </c>
     </row>
     <row r="17">
@@ -825,10 +825,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>14.98952004353151</v>
+        <v>14.49259840940244</v>
       </c>
       <c r="C17" t="n">
-        <v>1.05979037973021</v>
+        <v>1.105008627557268</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>96.34457997547359</v>
+        <v>100.4553297779335</v>
       </c>
     </row>
     <row r="18">
@@ -849,10 +849,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>16.04749855873573</v>
+        <v>15.59690381478543</v>
       </c>
       <c r="C18" t="n">
-        <v>1.057978515204223</v>
+        <v>1.104305405382988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>96.17986501856569</v>
+        <v>100.3914004893625</v>
       </c>
     </row>
     <row r="19">
@@ -873,10 +873,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>17.10340536937683</v>
+        <v>16.70080671099171</v>
       </c>
       <c r="C19" t="n">
-        <v>1.055906810641098</v>
+        <v>1.103902896206275</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>95.99152824009978</v>
+        <v>100.354808746025</v>
       </c>
     </row>
     <row r="20">
@@ -897,10 +897,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>18.1556290521891</v>
+        <v>17.80416451293284</v>
       </c>
       <c r="C20" t="n">
-        <v>1.052223682812269</v>
+        <v>1.103357801941137</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>95.65669843747897</v>
+        <v>100.3052547219215</v>
       </c>
     </row>
     <row r="21">
@@ -921,10 +921,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>19.20997154058639</v>
+        <v>18.9066816254796</v>
       </c>
       <c r="C21" t="n">
-        <v>1.054342488397296</v>
+        <v>1.102517112546753</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>95.84931712702691</v>
+        <v>100.2288284133412</v>
       </c>
     </row>
     <row r="22">
@@ -945,10 +945,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>20.26299732771692</v>
+        <v>20.00835414851035</v>
       </c>
       <c r="C22" t="n">
-        <v>1.053025787130522</v>
+        <v>1.101672523030757</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>95.72961701186567</v>
+        <v>100.1520475482506</v>
       </c>
     </row>
     <row r="23">
@@ -969,10 +969,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>21.31033341195971</v>
+        <v>21.10929865392855</v>
       </c>
       <c r="C23" t="n">
-        <v>1.047336084242794</v>
+        <v>1.100944505418198</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>95.21237129479941</v>
+        <v>100.0858641289271</v>
       </c>
     </row>
     <row r="24">
@@ -993,10 +993,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>22.35610598333428</v>
+        <v>22.20935616007882</v>
       </c>
       <c r="C24" t="n">
-        <v>1.045772571374567</v>
+        <v>1.100057506150264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>95.07023376132425</v>
+        <v>100.0052278318422</v>
       </c>
     </row>
     <row r="25">
@@ -1017,10 +1017,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>23.40056677922347</v>
+        <v>23.30885072692595</v>
       </c>
       <c r="C25" t="n">
-        <v>1.044460795889197</v>
+        <v>1.099494566847138</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>94.95098144447246</v>
+        <v>99.95405153155799</v>
       </c>
     </row>
     <row r="26">
@@ -1041,10 +1041,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>24.44359582009594</v>
+        <v>24.40767121329099</v>
       </c>
       <c r="C26" t="n">
-        <v>1.043029040872465</v>
+        <v>1.098820486365039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>94.82082189749683</v>
+        <v>99.8927714877308</v>
       </c>
     </row>
     <row r="27">
@@ -1065,10 +1065,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>25.4831948218273</v>
+        <v>25.50586794777845</v>
       </c>
       <c r="C27" t="n">
-        <v>1.039599001731357</v>
+        <v>1.098196734487459</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>94.5090001573961</v>
+        <v>99.83606677158717</v>
       </c>
     </row>
     <row r="28">
@@ -1089,10 +1089,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>26.52631445530069</v>
+        <v>26.60321975865625</v>
       </c>
       <c r="C28" t="n">
-        <v>1.043119633473388</v>
+        <v>1.097351810877797</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>94.82905758848985</v>
+        <v>99.75925553434514</v>
       </c>
     </row>
     <row r="29">
@@ -1113,10 +1113,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>27.5686670992941</v>
+        <v>27.69924910305312</v>
       </c>
       <c r="C29" t="n">
-        <v>1.042352643993418</v>
+        <v>1.096029344396872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>94.75933127212889</v>
+        <v>99.63903130880651</v>
       </c>
     </row>
     <row r="30">
@@ -1137,10 +1137,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>28.60979222529076</v>
+        <v>28.78304771385524</v>
       </c>
       <c r="C30" t="n">
-        <v>1.041125125996658</v>
+        <v>1.08379861080212</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>94.64773872696887</v>
+        <v>98.52714643655634</v>
       </c>
     </row>
     <row r="31">
@@ -1161,10 +1161,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>29.64938541586051</v>
+        <v>29.86089125304247</v>
       </c>
       <c r="C31" t="n">
-        <v>1.03959319056975</v>
+        <v>1.077843539187231</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>94.50847186997728</v>
+        <v>97.9857762897483</v>
       </c>
     </row>
     <row r="32">
@@ -1185,10 +1185,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>30.68792447367722</v>
+        <v>30.93516370280259</v>
       </c>
       <c r="C32" t="n">
-        <v>1.038539057816706</v>
+        <v>1.074272449760119</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>94.41264161970055</v>
+        <v>97.66113179637449</v>
       </c>
     </row>
     <row r="33">
@@ -1209,10 +1209,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>31.7263162152612</v>
+        <v>32.00667863670272</v>
       </c>
       <c r="C33" t="n">
-        <v>1.038391741583983</v>
+        <v>1.071514933900133</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>94.39924923490749</v>
+        <v>97.41044853637571</v>
       </c>
     </row>
     <row r="34">
@@ -1233,10 +1233,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>32.76338812831584</v>
+        <v>33.0767579630373</v>
       </c>
       <c r="C34" t="n">
-        <v>1.037071913054639</v>
+        <v>1.070079326334579</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>94.27926482314901</v>
+        <v>97.27993875768897</v>
       </c>
     </row>
     <row r="35">
@@ -1257,10 +1257,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>33.7987298481729</v>
+        <v>34.15648554158277</v>
       </c>
       <c r="C35" t="n">
-        <v>1.035341719857065</v>
+        <v>1.079727578545466</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>94.12197453246048</v>
+        <v>98.15705259504234</v>
       </c>
     </row>
     <row r="36">
@@ -1281,10 +1281,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>34.83270037940027</v>
+        <v>35.23833022797701</v>
       </c>
       <c r="C36" t="n">
-        <v>1.033970531227368</v>
+        <v>1.081844686394241</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>93.9973210206698</v>
+        <v>98.34951694493101</v>
       </c>
     </row>
     <row r="37">
@@ -1305,10 +1305,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>35.86574666724295</v>
+        <v>36.30958559777886</v>
       </c>
       <c r="C37" t="n">
-        <v>1.033046287842673</v>
+        <v>1.071255369801854</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>93.91329889478844</v>
+        <v>97.38685180016853</v>
       </c>
     </row>
     <row r="38">
@@ -1329,10 +1329,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>36.89740618197521</v>
+        <v>37.37492471677352</v>
       </c>
       <c r="C38" t="n">
-        <v>1.031659514732269</v>
+        <v>1.065339118994657</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>93.78722861202442</v>
+        <v>96.84901081769613</v>
       </c>
     </row>
     <row r="39">
@@ -1353,10 +1353,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>37.92829661484846</v>
+        <v>38.43806126470225</v>
       </c>
       <c r="C39" t="n">
-        <v>1.030890432873242</v>
+        <v>1.063136547928728</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>93.71731207938568</v>
+        <v>96.64877708442984</v>
       </c>
     </row>
     <row r="40">
@@ -1377,10 +1377,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>38.95850830029624</v>
+        <v>39.49974416627123</v>
       </c>
       <c r="C40" t="n">
-        <v>1.030211685447789</v>
+        <v>1.061682901568986</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>93.65560776798078</v>
+        <v>96.51662741536235</v>
       </c>
     </row>
     <row r="41">
@@ -1401,10 +1401,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>39.98860228884588</v>
+        <v>40.56061757267415</v>
       </c>
       <c r="C41" t="n">
-        <v>1.030093988549631</v>
+        <v>1.060873406402912</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>93.6449080499664</v>
+        <v>96.44303694571929</v>
       </c>
     </row>
     <row r="42">
@@ -1425,10 +1425,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>41.01705848167371</v>
+        <v>41.63114874496969</v>
       </c>
       <c r="C42" t="n">
-        <v>1.028456192827839</v>
+        <v>1.070531172295539</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>93.49601752980357</v>
+        <v>97.32101566323078</v>
       </c>
     </row>
     <row r="43">
@@ -1449,10 +1449,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>42.04438475344786</v>
+        <v>42.70383388345945</v>
       </c>
       <c r="C43" t="n">
-        <v>1.027326271774143</v>
+        <v>1.07268513848976</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>93.39329743401301</v>
+        <v>97.51683077179636</v>
       </c>
     </row>
     <row r="44">
@@ -1473,10 +1473,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>43.07010828743945</v>
+        <v>43.76889004370484</v>
       </c>
       <c r="C44" t="n">
-        <v>1.025723533991588</v>
+        <v>1.065056160245398</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>93.24759399923526</v>
+        <v>96.82328729503614</v>
       </c>
     </row>
     <row r="45">
@@ -1497,10 +1497,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>44.08658300417674</v>
+        <v>44.82625898474644</v>
       </c>
       <c r="C45" t="n">
-        <v>1.016474716737292</v>
+        <v>1.057368941041595</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>92.40679243066293</v>
+        <v>96.12444918559956</v>
       </c>
     </row>
     <row r="46">
@@ -1521,10 +1521,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>45.10024541836556</v>
+        <v>45.88284822358288</v>
       </c>
       <c r="C46" t="n">
-        <v>1.013662414188822</v>
+        <v>1.056589238836445</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>92.15112856262017</v>
+        <v>96.05356716694951</v>
       </c>
     </row>
     <row r="47">
@@ -1545,10 +1545,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>46.1126554106551</v>
+        <v>46.93851289681216</v>
       </c>
       <c r="C47" t="n">
-        <v>1.012409992289541</v>
+        <v>1.05566467322928</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>92.03727202632192</v>
+        <v>95.96951574811639</v>
       </c>
     </row>
     <row r="48">
@@ -1569,10 +1569,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>46.39238602108801</v>
+        <v>47.9926422861599</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2797306104329067</v>
+        <v>1.054129389347736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1585,22 +1585,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>25.4300554939006</v>
+        <v>95.8299444861578</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>1.160620725192767</v>
+        <v>49.05435303477396</v>
       </c>
       <c r="C49" t="n">
-        <v>1.160620725192767</v>
+        <v>1.061710748614061</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1609,22 +1609,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>105.5109750175243</v>
+        <v>96.51915896491464</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>1.145706012058183</v>
+        <v>50.11919434062645</v>
       </c>
       <c r="C50" t="n">
-        <v>1.145706012058183</v>
+        <v>1.064841305852489</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CS2_36</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1633,22 +1633,22 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>104.1550920052894</v>
+        <v>96.80375507749903</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>1.153332504667897</v>
+        <v>51.18325301816826</v>
       </c>
       <c r="C51" t="n">
-        <v>1.153332504667897</v>
+        <v>1.064058677541809</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CS2_37</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1657,22 +1657,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>104.8484095152634</v>
+        <v>96.73260704925532</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>1.134444845802931</v>
+        <v>52.23606753857995</v>
       </c>
       <c r="C52" t="n">
-        <v>1.134444845802931</v>
+        <v>1.052814520411694</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CS2_37</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1681,22 +1681,22 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>103.1313496184483</v>
+        <v>95.71041094651763</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>1.16241194625815</v>
+        <v>53.28768827080705</v>
       </c>
       <c r="C53" t="n">
-        <v>1.16241194625815</v>
+        <v>1.0516207322271</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1705,22 +1705,22 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>105.6738132961954</v>
+        <v>95.60188474791818</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>1.140773820517232</v>
+        <v>54.33830268728399</v>
       </c>
       <c r="C54" t="n">
-        <v>1.140773820517232</v>
+        <v>1.05061441647694</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CS2_38</t>
+          <t>CS2_35</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1729,30 +1729,1254 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>103.706710956112</v>
+        <v>95.51040149790359</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1.052322023911945</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1.052322023911945</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>95.66563853744955</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="n">
+        <v>2.149665492833128</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1.097343468921183</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>99.75849717465297</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="n">
+        <v>3.245035743823332</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1.095370250990204</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>99.57911372638219</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="n">
+        <v>4.3427396829912</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1.097703939167868</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>99.79126719707895</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="n">
+        <v>5.438155466960088</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1.095415783968887</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>99.58325308808065</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="n">
+        <v>6.408604373024617</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.9704489060645294</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>88.22262782404812</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="n">
+        <v>7.495652225355175</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1.087047852330558</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>98.82253203005074</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="n">
+        <v>8.577396784697651</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1.081744559342476</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>98.34041448567962</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="n">
+        <v>9.654946259914045</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1.077549475216394</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>97.95904320149033</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="n">
+        <v>10.72613836450355</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1.071192104589505</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>97.38110041722771</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="n">
+        <v>11.79860684954863</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1.072468485045077</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>97.49713500409788</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="n">
+        <v>12.86786434001764</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1.069257490469012</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>97.20522640627377</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="n">
+        <v>13.9297296638013</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1.061865323783662</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>96.53321125306019</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="n">
+        <v>14.98952004353151</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1.05979037973021</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>96.34457997547359</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="n">
+        <v>16.04749855873573</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1.057978515204223</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>96.17986501856569</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="n">
+        <v>17.10340536937683</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1.055906810641098</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>95.99152824009978</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="n">
+        <v>18.1556290521891</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1.052223682812269</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>95.65669843747897</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="n">
+        <v>19.20997154058639</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1.054342488397296</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>95.84931712702691</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="n">
+        <v>20.26299732771692</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1.053025787130522</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>95.72961701186567</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="n">
+        <v>21.31033341195971</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1.047336084242794</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>95.21237129479941</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="n">
+        <v>22.35610598333428</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1.045772571374567</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>95.07023376132425</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="n">
+        <v>23.40056677922347</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1.044460795889197</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>94.95098144447246</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="n">
+        <v>24.44359582009594</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1.043029040872465</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>94.82082189749683</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="n">
+        <v>25.4831948218273</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1.039599001731357</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>94.5090001573961</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="n">
+        <v>26.52631445530069</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1.043119633473388</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>94.82905758848985</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="n">
+        <v>27.5686670992941</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1.042352643993418</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>94.75933127212889</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="n">
+        <v>28.60979222529076</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1.041125125996658</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>94.64773872696887</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="n">
+        <v>29.64938541586051</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1.03959319056975</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>94.50847186997728</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="n">
+        <v>30.68792447367722</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1.038539057816706</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>94.41264161970055</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="n">
+        <v>31.7263162152612</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1.038391741583983</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>94.39924923490749</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="n">
+        <v>32.76338812831584</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1.037071913054639</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>94.27926482314901</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="n">
+        <v>33.7987298481729</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1.035341719857065</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>94.12197453246048</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="n">
+        <v>34.83270037940027</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1.033970531227368</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>93.9973210206698</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="n">
+        <v>35.86574666724295</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1.033046287842673</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>93.91329889478844</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="n">
+        <v>36.89740618197521</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1.031659514732269</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>93.78722861202442</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="n">
+        <v>37.92829661484846</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1.030890432873242</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>93.71731207938568</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="n">
+        <v>38.95850830029624</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1.030211685447789</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>93.65560776798078</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="n">
+        <v>39.98860228884588</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1.030093988549631</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>93.6449080499664</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="n">
+        <v>41.01705848167371</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1.028456192827839</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>93.49601752980357</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="n">
+        <v>42.04438475344786</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1.027326271774143</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>93.39329743401301</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="n">
+        <v>43.07010828743945</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1.025723533991588</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>93.24759399923526</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="n">
+        <v>44.08658300417674</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1.016474716737292</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>92.40679243066293</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="n">
+        <v>45.10024541836556</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1.013662414188822</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>92.15112856262017</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="n">
+        <v>46.1126554106551</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1.012409992289541</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>92.03727202632192</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="n">
+        <v>46.39238602108801</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.2797306104329067</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>CS2_35</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>25.4300554939006</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1</v>
+      </c>
+      <c r="B100" t="n">
+        <v>1.160620725192767</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1.160620725192767</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>105.5109750175243</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>2</v>
+      </c>
+      <c r="B101" t="n">
+        <v>1.145706012058183</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1.145706012058183</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CS2_36</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>104.1550920052894</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1</v>
+      </c>
+      <c r="B102" t="n">
+        <v>1.153332504667897</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1.153332504667897</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>104.8484095152634</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>2</v>
+      </c>
+      <c r="B103" t="n">
+        <v>1.134444845802931</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1.134444845802931</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>CS2_37</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>103.1313496184483</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1</v>
+      </c>
+      <c r="B104" t="n">
+        <v>1.16241194625815</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1.16241194625815</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>105.6738132961954</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2</v>
+      </c>
+      <c r="B105" t="n">
+        <v>1.140773820517232</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1.140773820517232</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>CS2_38</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>103.706710956112</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
         <v>3</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B106" t="n">
         <v>1.139105930615482</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C106" t="n">
         <v>1.139105930615482</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>CS2_38</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
         <v>103.5550846014075</v>
       </c>
     </row>
